--- a/naver-place-crawler/results_nail/청라_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청라_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>쏘네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>choseohyun041019@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1398-8291</t>
+          <t>0507-1371-4660</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>https://www.instagram.com/_sso_shop__/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>575</v>
+        <v>832</v>
       </c>
       <c r="Q2" t="n">
-        <v>824</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>1399</v>
+        <v>843</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>1293272639</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/1293272639</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>319</v>
+        <v>907</v>
       </c>
       <c r="Q3" t="n">
-        <v>116</v>
+        <v>380</v>
       </c>
       <c r="R3" t="n">
-        <v>435</v>
+        <v>1287</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>팡네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>nailppang@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1367-8073</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 염곡로498번길 6 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://www.instagram.com/pang___nail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>603</v>
+        <v>20</v>
       </c>
       <c r="Q4" t="n">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>731</v>
+        <v>40</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>2066386524</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/2066386524</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>446</v>
+        <v>258</v>
       </c>
       <c r="Q5" t="n">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="R5" t="n">
-        <v>611</v>
+        <v>287</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>어레브네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>anwlro9344@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1354-5482</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://blog.naver.com/anwlro9344</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>569</v>
+        <v>68</v>
       </c>
       <c r="Q6" t="n">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>702</v>
+        <v>73</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1364434683</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1364434683</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>네일리움</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dksdidwhdk@naver.com</t>
+          <t>nuy00@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1332-6316</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌 더 테라스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>http://pf.kakao.com/_JwDwK</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,17 +1072,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4a53h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>658</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>166</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>824</v>
+        <v>17</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1320367719</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1320367719</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>디얼유네일</t>
+          <t>네일도속눈썹</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dksdidwhdk@naver.com</t>
+          <t>naildorash1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1460-5911</t>
+          <t>0507-1395-6008</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 가정로 451 벨라미센텀시티2차 805호 디얼유</t>
+          <t>인천광역시 서구 염곡로 346-1 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dear.u_nail_?igsh=cTZxNWI0bGNsNWpk&amp;utm_source=qr</t>
+          <t>http://instagram.com/naildo_lash</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,17 +1166,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wwrcu0x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>139</v>
+        <v>404</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>289</v>
       </c>
       <c r="R8" t="n">
-        <v>151</v>
+        <v>693</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1516335621</t>
+          <t>1958392738</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1516335621</t>
+          <t>https://m.place.naver.com/place/1958392738</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>히온네일</t>
+          <t>네일바이윰 청라본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lololo988@naver.com</t>
+          <t>db-king@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1309-8247</t>
+          <t>0507-1409-8945</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 가정로 451 벨라미2차 1234호 히온네일</t>
+          <t>인천광역시 서구 청라루비로42번길 5-5 1층 101호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hion_nail/profilecard/?igsh=MWUzaDJkYm1vbWxo</t>
+          <t>https://www.instagram.com/nail_by.yoom</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1272,14 +1260,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmjx87a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1291,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>280</v>
+        <v>158</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1265061559</t>
+          <t>1031692471</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265061559</t>
+          <t>https://m.place.naver.com/place/1031692471</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1328,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>뷰티드시엘</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jysjysyessle@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1448-4452</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 27 221 일부호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_du_ciel</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1370,14 +1354,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r1kj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1389,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>173</v>
+        <v>611</v>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="R10" t="n">
-        <v>253</v>
+        <v>829</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1538853353</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538853353</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1426,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포쉬네일 홈플러스청라점</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>alth81@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1473-4177</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로 587 홈플러스 청라점 B1층</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_cheongna</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1468,14 +1448,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4s99j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1487,32 +1463,6118 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>58</v>
+        <v>314</v>
       </c>
       <c r="Q11" t="n">
+        <v>236</v>
+      </c>
+      <c r="R11" t="n">
+        <v>550</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1330577008</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1330577008</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>오늘의 네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>redcherry88@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1484-2578</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 담지로8번길 7-10 1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/0neulnail</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>134</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1312212877</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312212877</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>아지트밍</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>suni_hh@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1492-7763</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 지하1층 B101-1호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/suni_hh</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>433</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>118</v>
+      </c>
+      <c r="R13" t="n">
+        <v>551</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1742689242</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742689242</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>봄네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>nb98269@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1309-5732</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 8-10 청라봄빌딩 b106호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://instagram.com/bomnail_b106</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>55</v>
+      </c>
+      <c r="R14" t="n">
+        <v>168</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1235537458</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235537458</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>제이언니네 청라본점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>tory0413@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1332-6316</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>167</v>
+      </c>
+      <c r="R15" t="n">
+        <v>830</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1095756447</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1095756447</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>네일클로버</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1309-5041</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>212</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>220</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1024146721</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1024146721</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>츄네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>chuu_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1355-7059</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 103동 211호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_DyBJs</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>48</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1673851812</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1673851812</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>블링루원뷰티</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ball_11058@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1462-3543</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9</v>
+      </c>
+      <c r="R18" t="n">
+        <v>237</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1323823289</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1323823289</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>네일하롱</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mimmmm95_@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1438-1442</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.harong</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>534</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>36</v>
+      </c>
+      <c r="R19" t="n">
+        <v>570</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1264211104</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264211104</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>레푸스 청라점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dldeoqkr@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1337-0812</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>68</v>
+      </c>
+      <c r="R20" t="n">
+        <v>364</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1742485791</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742485791</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>꼼꼼네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mobi04@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1398-8291</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>572</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>834</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1406</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1090442730</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1090442730</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>뷰티드시엘</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jysjysyessle@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1448-4452</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beauty_du_ciel</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>80</v>
+      </c>
+      <c r="R22" t="n">
+        <v>253</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1538853353</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538853353</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>네일도래쉬도</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sine74@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1483-3118</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 1층 117호(네일도 래쉬도)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sHFoqY2f</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>18</v>
+      </c>
+      <c r="R23" t="n">
+        <v>97</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1685354839</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1685354839</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>포네하네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>forestnh@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1400-8523</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/forestnh</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>116</v>
+      </c>
+      <c r="R24" t="n">
+        <v>447</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1672609930</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1672609930</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>미미무드네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>findmyperfectdays@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1379-2451</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 지하1층 B동 111호 미미무드네일</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_NpBeG/chat</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q25" t="n">
         <v>41</v>
       </c>
-      <c r="R11" t="n">
-        <v>99</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1744657085</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1744657085</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="R25" t="n">
+        <v>194</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1587592784</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587592784</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>네일글로우</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cottonpp@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1460-8342</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>57</v>
+      </c>
+      <c r="R26" t="n">
+        <v>121</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2075971036</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2075971036</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>반스뷰티&amp;네일 청라점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dkfma48007@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1373-7577</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>97</v>
+      </c>
+      <c r="R27" t="n">
+        <v>295</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1751652203</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1751652203</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>굳띵네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hahahaam@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>070-4247-1016</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로163번길 12 1층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodthing.nail</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>12</v>
+      </c>
+      <c r="R28" t="n">
+        <v>66</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1194539605</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1194539605</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>네일할일 청라본점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nailart1227@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1385-4415</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로18번안길 20 102호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cheongna_nail</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>463</v>
+      </c>
+      <c r="R29" t="n">
+        <v>509</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1006118353</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006118353</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>딩가네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>yejiiik@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1327-6084</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 210호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dinga_nail</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>17</v>
+      </c>
+      <c r="R30" t="n">
+        <v>203</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1879647738</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1879647738</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>힝네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>zoe0406@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로42번길 5-5 105호 힝네일,</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hing_nail/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>11</v>
+      </c>
+      <c r="R31" t="n">
+        <v>460</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1715411307</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1715411307</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>네일또온나 청라점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2xmania2xj@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1338-3150</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_tto_onna</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>63</v>
+      </c>
+      <c r="R32" t="n">
+        <v>310</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1546215593</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1546215593</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1248네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1248nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1479-8978</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/1248_nail</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>453</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>267</v>
+      </c>
+      <c r="R33" t="n">
+        <v>720</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1537239618</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1537239618</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>가비앤네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jmoh95@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1351-4914</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_XKZexj</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>31</v>
+      </c>
+      <c r="R34" t="n">
+        <v>331</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1145821785</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1145821785</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>르씨엘뷰티</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0728helen@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1376-4100</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌더테라스 상가 102동 2층 239호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>http://instagram.com/b_le_ciel</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>145</v>
+      </c>
+      <c r="R35" t="n">
+        <v>389</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1826304139</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1826304139</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>민블리네일</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>eun301010_@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-8 . 1층 109호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_thelove?igsh=MTloYm44ZHd2OHZmdw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>49</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1370458509</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370458509</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>네일소소</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>rkswlwoddl84@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1415-2417</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_so_so</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>20</v>
+      </c>
+      <c r="R37" t="n">
+        <v>291</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1394957062</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1394957062</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>네일드림</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>shsally0122@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1335-1809</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>http://instagram.com/naild_lim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>364</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1192065742</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192065742</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>푸스케어 청라점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>miwha2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1305-8118</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 76 1층 130호 FUSSCARE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/miwha2000</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>106</v>
+      </c>
+      <c r="R39" t="n">
+        <v>222</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1900780465</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1900780465</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>감성네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gamseongnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1424-4545</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gam_seongnail/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>165</v>
+      </c>
+      <c r="R40" t="n">
+        <v>613</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1382824710</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1382824710</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>트윈스네일</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>form2030@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1309-9545</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 122호 트윈스네일</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/form2030</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>27</v>
+      </c>
+      <c r="R41" t="n">
+        <v>132</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1102751111</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1102751111</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>네일무디크</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>e5174@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1375-3428</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_moodique</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>177</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1811715033</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1811715033</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>의미를 그리다</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>yunjbutton@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1349-2389</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스오피스텔 상가 A동 1층 상가안쪽</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/draw_meaning_nail</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>79</v>
+      </c>
+      <c r="R43" t="n">
+        <v>343</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1285622660</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285622660</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>디오뜨네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>younge_dailylife@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1363-3686</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 138호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_KBxhGn</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>9</v>
+      </c>
+      <c r="R44" t="n">
+        <v>216</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1228012496</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228012496</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>이르미네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jungsumi21@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1391-3129</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ezxgrG</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>107</v>
+      </c>
+      <c r="R45" t="n">
+        <v>341</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1596414337</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1596414337</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>제이제이네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>yang4550@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1319-1270</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jj__nail___</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>98</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2011413114</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2011413114</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>오늘의기분 네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bae_tamine@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1307-8929</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pxcsgb</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>77</v>
+      </c>
+      <c r="R47" t="n">
+        <v>425</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1747055394</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1747055394</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>유네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>luvu1016@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 78 엘림아트센터 304호 일부호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yu_nail_salon</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>15</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2051656387</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2051656387</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>섬세하나네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sumsehana@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1481-0788</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sumsehana</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>615</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>131</v>
+      </c>
+      <c r="R49" t="n">
+        <v>746</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1251340543</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251340543</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>네일서안</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>chorong-e-@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1367-5100</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.seoan</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>311</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>22</v>
+      </c>
+      <c r="R50" t="n">
+        <v>333</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1300004606</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1300004606</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>뷰티라운지케이 네일속눈썹피부 청라가정점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>beautylounge-k@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1467-7707</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 11-3 1층 뷰티라운지케이</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beautyloungek</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>103</v>
+      </c>
+      <c r="R51" t="n">
+        <v>360</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1706279657</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706279657</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일그리미</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>tory0413@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1346-5358</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.grimmy</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>54</v>
+      </c>
+      <c r="R52" t="n">
+        <v>403</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1125220368</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125220368</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>네일에딧</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>byddooroo@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>779</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>6</v>
+      </c>
+      <c r="R53" t="n">
+        <v>785</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2041818773</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041818773</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>에스영이네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>s02nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1322-9488</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_JAxdFs</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>188</v>
+      </c>
+      <c r="R54" t="n">
+        <v>614</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1726483094</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726483094</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>네일, 안느</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gkswngml3594@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1403-9410</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로7번길 14 1층 102호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/0n_anne</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>214</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>17</v>
+      </c>
+      <c r="R55" t="n">
+        <v>231</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1256153031</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1256153031</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>미드미네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dreaming_yjso@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1309-9513</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로144번길 23 미드미네일</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_kVxoJxj</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>20</v>
+      </c>
+      <c r="R56" t="n">
+        <v>69</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1581342551</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1581342551</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>라나뷰티 청라본점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>yellowground_@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1392-1325</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_rananail</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>459</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>25</v>
+      </c>
+      <c r="R57" t="n">
+        <v>484</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1071013615</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1071013615</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>온더네일 앤 스킨</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sing1228@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1444-7836</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 가정로 437 SK리더스뷰 301동 302호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/on_the_nail302</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8</v>
+      </c>
+      <c r="R58" t="n">
+        <v>61</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1782633744</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782633744</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>네일,미</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>specialjee@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1476-4143</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로233번길 3-4 103호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ytyub</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>38</v>
+      </c>
+      <c r="R59" t="n">
+        <v>395</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1645376518</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1645376518</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>프롬쥬네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dlaalswn89@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1327-0666</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlaalswn89</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>567</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>134</v>
+      </c>
+      <c r="R60" t="n">
+        <v>701</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1545913000</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1545913000</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>보라네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>00bora00@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1494-0141</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로138번길 10 1층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bora_nail__</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>15</v>
+      </c>
+      <c r="R61" t="n">
+        <v>204</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>37700904</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37700904</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일퐁</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>aksk1313@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1315-1372</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로8번안길 4 1층 일부호(103호)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nailpong</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>135</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2035104802</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2035104802</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>인생네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>askflclsrna@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1301-5228</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/life_nail_salon</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>11</v>
+      </c>
+      <c r="R63" t="n">
+        <v>361</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1764464663</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1764464663</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 상가A동 223호 COCO.NAIL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coco.nail_._?igsh=MXIydzZsZ2M3eGVmZw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>19</v>
+      </c>
+      <c r="R64" t="n">
+        <v>94</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1165395528</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1165395528</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>네일을기억해</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>rimo0904@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1491-7279</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/remember._nails</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>44</v>
+      </c>
+      <c r="R65" t="n">
+        <v>254</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1811328950</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1811328950</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>로미네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0rominail0@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1443-7127</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 1층 091호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ro.mi_nail</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>77</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2072431299</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072431299</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>네일,맑음</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sh2066@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1350-4484</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로144번길 6-8 1층 네일,맑음</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_NxlhEn</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>20</v>
+      </c>
+      <c r="R67" t="n">
+        <v>320</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1051767791</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1051767791</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>쏠네일</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>hansol5992@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>070-7612-9500</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매5동 203호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ssol_nail</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>77</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1187656534</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1187656534</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>단감네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>aayoon7@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1374-8432</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dangam_nail/</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>337</v>
+      </c>
+      <c r="R69" t="n">
+        <v>542</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1985862694</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1985862694</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>오늘도네일도</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>nail_oneul@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1449-7506</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_oneul</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>813</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>42</v>
+      </c>
+      <c r="R70" t="n">
+        <v>855</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1810678383</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1810678383</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일달다 청라점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>haru_log_in@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1325-3255</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://instagram.com/naildalda_</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>239</v>
+      </c>
+      <c r="R71" t="n">
+        <v>861</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1040857451</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040857451</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>마이즈네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>flyue@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1417-2584</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로144번길 19 . 1층 마이즈네일</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_BMRfG</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4</v>
+      </c>
+      <c r="R72" t="n">
+        <v>184</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1176695071</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176695071</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>와우뷰티 청라점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>e5174@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1323-1043</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>49</v>
+      </c>
+      <c r="R73" t="n">
+        <v>140</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1012993987</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012993987</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일델루나</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>eatingzzz@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1358-7017</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_delluna</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1526</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>15</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1541</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1852644091</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1852644091</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>도르네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>bnm4818@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>721</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>53</v>
+      </c>
+      <c r="R75" t="n">
+        <v>774</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1001824596</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1001824596</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>블링뷰네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>bv_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1350-9502</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_RqUxcG</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>153</v>
+      </c>
+      <c r="R76" t="n">
+        <v>270</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1259415075</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1259415075</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/청라_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청라_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>619</v>
+        <v>664</v>
       </c>
       <c r="Q2" t="n">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="R2" t="n">
-        <v>750</v>
+        <v>831</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>오늘의 네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>redcherry88@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1484-2578</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 담지로8번길 7-10 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://www.instagram.com/0neulnail</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>314</v>
+        <v>130</v>
       </c>
       <c r="Q3" t="n">
-        <v>262</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>576</v>
+        <v>135</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1312212877</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1312212877</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>336</v>
+        <v>234</v>
       </c>
       <c r="Q4" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="R4" t="n">
-        <v>452</v>
+        <v>342</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bae_tamine@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>353</v>
+        <v>610</v>
       </c>
       <c r="Q5" t="n">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="R5" t="n">
-        <v>430</v>
+        <v>828</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,34 +940,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1398-8291</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>572</v>
+        <v>797</v>
       </c>
       <c r="Q6" t="n">
-        <v>843</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1415</v>
+        <v>803</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1030,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>에스영이네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>s02nail@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>0507-1322-9488</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>http://pf.kakao.com/_JAxdFs</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="Q7" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="R7" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1726483094</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1726483094</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>디오뜨네일 청라본점</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>younge_dailylife@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1363-3686</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 서구 중봉대로612번길 10-17 1층 138호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KBxhGn</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1170,17 +1166,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w6geumc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1228012496</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228012496</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아트스타일네일</t>
+          <t>블링루원뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gotitkorea@naver.com</t>
+          <t>ball_11058@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1418-1574</t>
+          <t>0507-1462-3543</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 서구 염곡로464번길 30 416호</t>
+          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artstyle__nail?igsh=MXJ6amo4eWJtZWZkcw==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,7 +1250,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1268,14 +1260,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fqs68</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="Q9" t="n">
-        <v>296</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>413</v>
+        <v>237</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1976908458</t>
+          <t>1323823289</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976908458</t>
+          <t>https://m.place.naver.com/place/1323823289</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,39 +1312,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일서안</t>
+          <t>도르네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chorong-e-@naver.com</t>
+          <t>bnm4818@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1367-5100</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.seoan</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1366,14 +1350,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45pkk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1385,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>312</v>
+        <v>728</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>334</v>
+        <v>782</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1300004606</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300004606</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1422,30 +1402,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유네일</t>
+          <t>네일서안</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>luvu1016@naver.com</t>
+          <t>chorong-e-@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1367-5100</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 서구 크리스탈로 78 엘림아트센터 304호 일부호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yu_nail_salon</t>
+          <t>https://www.instagram.com/nail.seoan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1455,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1475,30 +1459,6116 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22</v>
+      </c>
+      <c r="R11" t="n">
+        <v>334</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1300004606</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1300004606</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>민블리네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>eun301010_@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-8 . 1층 109호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_thelove?igsh=MTloYm44ZHd2OHZmdw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>50</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1370458509</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370458509</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>네일, 안느</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gkswngml3594@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1403-9410</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로7번길 14 1층 102호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/0n_anne</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>17</v>
+      </c>
+      <c r="R13" t="n">
+        <v>232</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1256153031</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1256153031</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>마이즈네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flyue@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1417-2584</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로144번길 19 . 1층 마이즈네일</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_BMRfG</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>184</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1176695071</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176695071</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>네일달다 청라점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>haru_log_in@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1325-3255</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://instagram.com/naildalda_</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>239</v>
+      </c>
+      <c r="R15" t="n">
+        <v>861</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1040857451</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040857451</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>블링뷰네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bv_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1350-9502</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_RqUxcG</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>153</v>
+      </c>
+      <c r="R16" t="n">
+        <v>270</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1259415075</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1259415075</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>미드미네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dreaming_yjso@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1309-9513</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로144번길 23 미드미네일</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_kVxoJxj</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" t="n">
+        <v>70</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1581342551</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1581342551</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>섬세하나네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sumsehana@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1481-0788</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sumsehana</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>619</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>131</v>
+      </c>
+      <c r="R18" t="n">
+        <v>750</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1251340543</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251340543</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>쏠네일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hansol5992@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>070-7612-9500</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매5동 203호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ssol_nail</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>77</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1187656534</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1187656534</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>츄네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>chuu_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1355-7059</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 103동 211호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_DyBJs</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>48</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1673851812</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1673851812</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>morningapple6@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1386-7822</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 B동 1층 026호 Jnail</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/j_nail21</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1404214241</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404214241</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>힝네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>zoe0406@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로42번길 5-5 105호 힝네일,</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hing_nail/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11</v>
+      </c>
+      <c r="R22" t="n">
+        <v>460</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1715411307</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1715411307</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>포네하네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>forestnh@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1400-8523</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/forestnh</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>116</v>
+      </c>
+      <c r="R23" t="n">
+        <v>452</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1672609930</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1672609930</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>단감네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sytf170@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1374-8432</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dangam_nail/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>337</v>
+      </c>
+      <c r="R24" t="n">
+        <v>544</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1985862694</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1985862694</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>꼼꼼네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mobi04@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1398-8291</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>572</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>843</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1415</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1090442730</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1090442730</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>네일퐁</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>aksk1313@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1315-1372</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 푸른로8번안길 4 1층 일부호(103호)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nailpong</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>136</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2035104802</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2035104802</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>트윈스네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>form2030@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1309-9545</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 122호 트윈스네일</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/form2030</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>27</v>
+      </c>
+      <c r="R27" t="n">
+        <v>132</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1102751111</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1102751111</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>네일리움</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>nuy00@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌 더 테라스</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_JwDwK</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>17</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1320367719</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320367719</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>코코네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jjuahlee@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 상가A동 223호 COCO.NAIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coco.nail_._?igsh=MXIydzZsZ2M3eGVmZw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>19</v>
+      </c>
+      <c r="R29" t="n">
+        <v>94</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1165395528</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1165395528</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>딩가네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>yejiiik@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1327-6084</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 210호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dinga_nail</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>17</v>
+      </c>
+      <c r="R30" t="n">
+        <v>203</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1879647738</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1879647738</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>로미네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0rominail0@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1443-7127</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 1층 091호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ro.mi_nail</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>78</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2072431299</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072431299</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>디오뜨네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>younge_dailylife@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1363-3686</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 138호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_KBxhGn</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9</v>
+      </c>
+      <c r="R32" t="n">
+        <v>216</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1228012496</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228012496</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>굳띵네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hahahaam@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>070-4247-1016</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로163번길 12 1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodthing.nail</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>66</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1194539605</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1194539605</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>뷰티라운지케이 네일속눈썹피부 청라가정점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>beautylounge-k@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1467-7707</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 11-3 1층 뷰티라운지케이</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beautyloungek</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>103</v>
+      </c>
+      <c r="R34" t="n">
+        <v>360</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1706279657</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706279657</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>라나뷰티 청라본점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>yellowground_@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1392-1325</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_rananail</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>460</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>25</v>
+      </c>
+      <c r="R35" t="n">
+        <v>485</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1071013615</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1071013615</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>네일무디크</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>e5174@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1375-3428</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_moodique</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>9</v>
+      </c>
+      <c r="R36" t="n">
+        <v>177</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1811715033</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1811715033</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>가비앤네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jmoh95@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1351-4914</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_XKZexj</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>31</v>
+      </c>
+      <c r="R37" t="n">
+        <v>331</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1145821785</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1145821785</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>쏘네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>choseohyun041019@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1371-4660</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_sso_shop__/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>834</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>11</v>
+      </c>
+      <c r="R38" t="n">
+        <v>845</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1293272639</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293272639</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>네일도래쉬도</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>suging324@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1483-3118</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 1층 117호(네일도 래쉬도)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sHFoqY2f</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>18</v>
+      </c>
+      <c r="R39" t="n">
+        <v>97</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1685354839</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1685354839</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>반스뷰티&amp;네일 청라점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dkfma48007@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1373-7577</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>97</v>
+      </c>
+      <c r="R40" t="n">
+        <v>295</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1751652203</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1751652203</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>봄네일</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>nb98269@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1309-5732</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 8-10 청라봄빌딩 b106호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>http://instagram.com/bomnail_b106</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>55</v>
+      </c>
+      <c r="R41" t="n">
+        <v>168</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1235537458</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235537458</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>레푸스 청라점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dldeoqkr@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1337-0812</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>68</v>
+      </c>
+      <c r="R42" t="n">
+        <v>369</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1742485791</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742485791</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>보라네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>00bora00@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1494-0141</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로138번길 10 1층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bora_nail__</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>15</v>
+      </c>
+      <c r="R43" t="n">
+        <v>204</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>37700904</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37700904</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>네일,맑음</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sh2066@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1350-4484</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로144번길 6-8 1층 네일,맑음</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_NxlhEn</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>20</v>
+      </c>
+      <c r="R44" t="n">
+        <v>320</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1051767791</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1051767791</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>뷰티드시엘</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jysjysyessle@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1448-4452</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beauty_du_ciel</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>80</v>
+      </c>
+      <c r="R45" t="n">
+        <v>253</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1538853353</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538853353</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>오늘의기분 네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bae_tamine@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1307-8929</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pxcsgb</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>77</v>
+      </c>
+      <c r="R46" t="n">
+        <v>430</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1747055394</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1747055394</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>미미무드네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>findmyperfectdays@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1379-2451</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 지하1층 B동 111호 미미무드네일</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_NpBeG/chat</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>41</v>
+      </c>
+      <c r="R47" t="n">
+        <v>195</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1587592784</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587592784</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>네일위드유 문제성발톱 속눈썹</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nail_with_yoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1344-1735</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_with_yoo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>29</v>
+      </c>
+      <c r="R48" t="n">
+        <v>288</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1776289071</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1776289071</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>네일소소</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>rkswlwoddl84@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1415-2417</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_so_so</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>20</v>
+      </c>
+      <c r="R49" t="n">
+        <v>291</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1394957062</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1394957062</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>네일그리미</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>tory0413@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1346-5358</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.grimmy</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>54</v>
+      </c>
+      <c r="R50" t="n">
+        <v>403</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1125220368</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125220368</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>르씨엘뷰티</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0728helen@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1376-4100</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌더테라스 상가 102동 2층 239호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>http://instagram.com/b_le_ciel</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>145</v>
+      </c>
+      <c r="R51" t="n">
+        <v>391</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1826304139</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1826304139</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일할일 청라본점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nailart1227@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1385-4415</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 보석로18번안길 20 102호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cheongna_nail</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>463</v>
+      </c>
+      <c r="R52" t="n">
+        <v>509</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1006118353</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006118353</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>팡네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nailppang@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1367-8073</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번길 6 1층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pang___nail</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>20</v>
+      </c>
+      <c r="R53" t="n">
+        <v>40</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2066386524</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066386524</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>네일,미</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>specialjee@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1476-4143</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로233번길 3-4 103호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ytyub</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>38</v>
+      </c>
+      <c r="R54" t="n">
+        <v>395</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1645376518</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1645376518</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>요네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>yunjin0313@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로612번길 10 103호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/yo_nailshop</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>512</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>33</v>
+      </c>
+      <c r="R55" t="n">
+        <v>545</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1271412561</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1271412561</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>네일델루나</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>eatingzzz@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1358-7017</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_delluna</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1534</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>15</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1549</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1852644091</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1852644091</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>푸스케어 청라점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>miwha2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1305-8118</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로 76 1층 130호 FUSSCARE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/miwha2000</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>106</v>
+      </c>
+      <c r="R57" t="n">
+        <v>222</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1900780465</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1900780465</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>어레브네일</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>anwlro9344@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1354-5482</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/anwlro9344</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>74</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1364434683</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1364434683</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>프롬쥬네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dlaalswn89@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1327-0666</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlaalswn89</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>567</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>133</v>
+      </c>
+      <c r="R59" t="n">
+        <v>700</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1545913000</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1545913000</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>아이퀸네일 청라점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gamejaki@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1351-6212</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>314</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>266</v>
+      </c>
+      <c r="R60" t="n">
+        <v>580</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1330577008</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1330577008</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>와우뷰티 청라점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>e5174@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1323-1043</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>49</v>
+      </c>
+      <c r="R61" t="n">
+        <v>140</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1012993987</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012993987</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>01192291122@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1338-0068</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/01192291122</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>907</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>380</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1287</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1868333219</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868333219</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1248네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1248nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1479-8978</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/1248_nail</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>456</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>267</v>
+      </c>
+      <c r="R63" t="n">
+        <v>723</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1537239618</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1537239618</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>오늘도네일도</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nail_oneul@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1449-7506</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_oneul</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>815</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>42</v>
+      </c>
+      <c r="R64" t="n">
+        <v>857</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1810678383</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1810678383</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>인생네일 청라본점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>askflclsrna@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1301-5228</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/life_nail_salon</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>11</v>
+      </c>
+      <c r="R65" t="n">
+        <v>362</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1764464663</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1764464663</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>의미를 그리다</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>yunjbutton@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1349-2389</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스오피스텔 상가 A동 1층 상가안쪽</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/draw_meaning_nail</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>79</v>
+      </c>
+      <c r="R66" t="n">
+        <v>343</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1285622660</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285622660</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>유네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>luvu1016@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 크리스탈로 78 엘림아트센터 304호 일부호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yu_nail_salon</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
         <v>14</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q67" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R67" t="n">
         <v>15</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
         <is>
           <t>2051656387</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2051656387</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네일글로우</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>cottonpp@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1460-8342</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>56</v>
+      </c>
+      <c r="R68" t="n">
+        <v>120</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2075971036</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2075971036</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네일바이윰 청라본점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>db-king@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1409-8945</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라루비로42번길 5-5 1층 101호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by.yoom</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2</v>
+      </c>
+      <c r="R69" t="n">
+        <v>158</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1031692471</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1031692471</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일을기억해</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>rimo0904@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1491-7279</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/remember._nails</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>44</v>
+      </c>
+      <c r="R70" t="n">
+        <v>254</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1811328950</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1811328950</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일또온나 청라점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2xmania2xj@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1338-3150</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_tto_onna</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>63</v>
+      </c>
+      <c r="R71" t="n">
+        <v>310</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1546215593</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1546215593</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>네일드림</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>shsally0122@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1335-1809</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>http://instagram.com/naild_lim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>356</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>8</v>
+      </c>
+      <c r="R72" t="n">
+        <v>364</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1192065742</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192065742</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>아지트밍</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>suni_hh@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1492-7763</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 지하1층 B101-1호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/suni_hh</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>434</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>118</v>
+      </c>
+      <c r="R73" t="n">
+        <v>552</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1742689242</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742689242</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>감성네일</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gamseongnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1424-4545</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gam_seongnail/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>164</v>
+      </c>
+      <c r="R74" t="n">
+        <v>612</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1382824710</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1382824710</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>제이제이네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>yang4550@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1319-1270</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jj__nail___</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>100</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2011413114</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2011413114</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>네일하롱</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>mimmmm95_@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1438-1442</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.harong</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>536</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>36</v>
+      </c>
+      <c r="R76" t="n">
+        <v>572</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1264211104</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264211104</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_nail/청라_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청라_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>보라네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>00bora00@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1332-6316</t>
+          <t>0507-1494-0141</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 청라라임로138번길 10 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>https://www.instagram.com/bora_nail__</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>664</v>
+        <v>189</v>
       </c>
       <c r="Q2" t="n">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="R2" t="n">
-        <v>831</v>
+        <v>204</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>37700904</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/37700904</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q3" t="n">
         <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이르미네일</t>
+          <t>민블리네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>aboutdanchuu@naver.com</t>
+          <t>eun301010_@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1391-3129</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 중봉대로612번길 10-8 . 1층 109호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>https://www.instagram.com/nail_thelove?igsh=MTloYm44ZHd2OHZmdw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>234</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>342</v>
+        <v>50</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>1370458509</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/1370458509</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>네일을기억해</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dlgufl0924@naver.com</t>
+          <t>rimo0904@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1408-0807</t>
+          <t>0507-1491-7279</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>https://www.instagram.com/remember._nails</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>610</v>
+        <v>210</v>
       </c>
       <c r="Q5" t="n">
-        <v>218</v>
+        <v>44</v>
       </c>
       <c r="R5" t="n">
-        <v>828</v>
+        <v>254</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>1811328950</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/1811328950</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일에딧</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>byddooroo@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -953,17 +949,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+          <t>인천광역시 서구 청라라임로 85 상가A동 223호 COCO.NAIL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dZxhxcn</t>
+          <t>https://www.instagram.com/coco.nail_._?igsh=MXIydzZsZ2M3eGVmZw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -984,7 +980,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>797</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
-        <v>803</v>
+        <v>98</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2041818773</t>
+          <t>1165395528</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041818773</t>
+          <t>https://m.place.naver.com/place/1165395528</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,34 +1026,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에스영이네일</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>s02nail@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1322-9488</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JAxdFs</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1078,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>427</v>
+        <v>351</v>
       </c>
       <c r="Q7" t="n">
-        <v>188</v>
+        <v>11</v>
       </c>
       <c r="R7" t="n">
-        <v>615</v>
+        <v>362</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1726483094</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726483094</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일클로버</t>
+          <t>네일글로우</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>cottonpp@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1309-5041</t>
+          <t>0507-1460-8342</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>221</v>
+        <v>120</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>2075971036</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/2075971036</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,39 +1214,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>블링루원뷰티</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ball_11058@naver.com</t>
+          <t>mina20624@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1462-3543</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>228</v>
+        <v>665</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="R9" t="n">
-        <v>237</v>
+        <v>832</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1323823289</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323823289</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1312,40 +1308,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>도르네일</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bnm4818@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1481-0788</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>728</v>
+        <v>620</v>
       </c>
       <c r="Q10" t="n">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="R10" t="n">
-        <v>782</v>
+        <v>751</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일서안</t>
+          <t>네일, 안느</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chorong-e-@naver.com</t>
+          <t>gkswngml3594@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1367-5100</t>
+          <t>0507-1403-9410</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
+          <t>인천광역시 서구 푸른로7번길 14 1층 102호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.seoan</t>
+          <t>https://www.instagram.com/0n_anne</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>312</v>
+        <v>215</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>334</v>
+        <v>232</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1300004606</t>
+          <t>1256153031</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300004606</t>
+          <t>https://m.place.naver.com/place/1256153031</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,30 +1496,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>민블리네일</t>
+          <t>가비앤네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eun301010_@naver.com</t>
+          <t>jmoh95@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1351-4914</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-8 . 1층 109호</t>
+          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_thelove?igsh=MTloYm44ZHd2OHZmdw%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_XKZexj</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1540,7 +1544,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>301</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="R12" t="n">
-        <v>50</v>
+        <v>332</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1370458509</t>
+          <t>1145821785</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370458509</t>
+          <t>https://m.place.naver.com/place/1145821785</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1590,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일, 안느</t>
+          <t>봄네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gkswngml3594@naver.com</t>
+          <t>nb98269@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1403-9410</t>
+          <t>0507-1309-5732</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로7번길 14 1층 102호</t>
+          <t>인천광역시 서구 청라커낼로288번길 8-10 청라봄빌딩 b106호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/0n_anne</t>
+          <t>http://instagram.com/bomnail_b106</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1643,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>215</v>
+        <v>113</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="R13" t="n">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1256153031</t>
+          <t>1235537458</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256153031</t>
+          <t>https://m.place.naver.com/place/1235537458</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1680,34 +1684,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>마이즈네일</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flyue@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1417-2584</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 19 . 1층 마이즈네일</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_BMRfG</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1717,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1728,7 +1732,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1737,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>567</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="R14" t="n">
-        <v>184</v>
+        <v>700</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1176695071</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176695071</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
+          <t>아지트밍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>haru_log_in@naver.com</t>
+          <t>suni_hh@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1492-7763</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 지하1층 B101-1호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://blog.naver.com/suni_hh</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1811,7 +1815,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1831,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>622</v>
+        <v>434</v>
       </c>
       <c r="Q15" t="n">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="R15" t="n">
-        <v>861</v>
+        <v>552</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>1742689242</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/1742689242</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>네일,맑음</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>sh2066@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1350-9502</t>
+          <t>0507-1350-4484</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 청라루비로144번길 6-8 1층 네일,맑음</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>https://pf.kakao.com/_NxlhEn</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1925,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>117</v>
+        <v>300</v>
       </c>
       <c r="Q16" t="n">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>1051767791</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/1051767791</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1962,34 +1966,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>미드미네일</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dreaming_yjso@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1309-9513</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 23 미드미네일</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kVxoJxj</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2010,7 +2014,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2019,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R17" t="n">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1581342551</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581342551</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>푸스케어 청라점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>miwha2000@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1305-8118</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라루비로 76 1층 130호 FUSSCARE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://blog.naver.com/miwha2000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>619</v>
+        <v>116</v>
       </c>
       <c r="Q18" t="n">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="R18" t="n">
-        <v>750</v>
+        <v>222</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1900780465</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1900780465</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>쏠네일</t>
+          <t>로미네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hansol5992@naver.com</t>
+          <t>0rominail0@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>070-7612-9500</t>
+          <t>0507-1443-7127</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매5동 203호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 1층 091호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssol_nail</t>
+          <t>https://www.instagram.com/ro.mi_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2211,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1187656534</t>
+          <t>2072431299</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187656534</t>
+          <t>https://m.place.naver.com/place/2072431299</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2248,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>츄네일</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>chuu_nail@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1355-7059</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 103동 211호</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DyBJs</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44</v>
+        <v>801</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>48</v>
+        <v>807</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1673851812</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673851812</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>르씨엘뷰티</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>morningapple6@naver.com</t>
+          <t>0728helen@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1386-7822</t>
+          <t>0507-1376-4100</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 B동 1층 026호 Jnail</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌더테라스 상가 102동 2층 239호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_nail21</t>
+          <t>http://instagram.com/b_le_ciel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7</v>
+        <v>246</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="R21" t="n">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1404214241</t>
+          <t>1826304139</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404214241</t>
+          <t>https://m.place.naver.com/place/1826304139</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2432,25 +2432,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>힝네일</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>zoe0406@naver.com</t>
+          <t>mobi04@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1398-8291</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로42번길 5-5 105호 힝네일,</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hing_nail/</t>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,13 +2489,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>449</v>
+        <v>573</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>846</v>
       </c>
       <c r="R22" t="n">
-        <v>460</v>
+        <v>1419</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1715411307</t>
+          <t>1090442730</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1715411307</t>
+          <t>https://m.place.naver.com/place/1090442730</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2522,29 +2526,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1479-8978</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2559,7 +2563,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2579,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>336</v>
+        <v>457</v>
       </c>
       <c r="Q23" t="n">
-        <v>116</v>
+        <v>267</v>
       </c>
       <c r="R23" t="n">
-        <v>452</v>
+        <v>724</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2598,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2616,39 +2620,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>단감네일</t>
+          <t>도르네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sytf170@naver.com</t>
+          <t>bnm4818@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1374-8432</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2673,13 +2673,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>207</v>
+        <v>728</v>
       </c>
       <c r="Q24" t="n">
-        <v>337</v>
+        <v>54</v>
       </c>
       <c r="R24" t="n">
-        <v>544</v>
+        <v>782</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2710,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>오늘도네일도</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>nail_oneul@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1398-8291</t>
+          <t>0507-1449-7506</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>572</v>
+        <v>815</v>
       </c>
       <c r="Q25" t="n">
-        <v>843</v>
+        <v>42</v>
       </c>
       <c r="R25" t="n">
-        <v>1415</v>
+        <v>857</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2782,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일퐁</t>
+          <t>어레브네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>aksk1313@naver.com</t>
+          <t>anwlro9344@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1315-1372</t>
+          <t>0507-1354-5482</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로8번안길 4 1층 일부호(103호)</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailpong</t>
+          <t>https://blog.naver.com/anwlro9344</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2035104802</t>
+          <t>1364434683</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035104802</t>
+          <t>https://m.place.naver.com/place/1364434683</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2898,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>트윈스네일</t>
+          <t>팡네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>form2030@naver.com</t>
+          <t>nailppang@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1309-9545</t>
+          <t>0507-1367-8073</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 1층 122호 트윈스네일</t>
+          <t>인천광역시 서구 염곡로498번길 6 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/form2030</t>
+          <t>https://www.instagram.com/pang___nail</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="Q27" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2970,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1102751111</t>
+          <t>2066386524</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102751111</t>
+          <t>https://m.place.naver.com/place/2066386524</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2992,30 +2992,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일리움</t>
+          <t>반스뷰티&amp;네일 청라점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nuy00@naver.com</t>
+          <t>dkfma48007@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1373-7577</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌 더 테라스</t>
+          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JwDwK</t>
+          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3045,13 +3049,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>198</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="R28" t="n">
-        <v>17</v>
+        <v>295</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3060,17 +3064,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1320367719</t>
+          <t>1751652203</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320367719</t>
+          <t>https://m.place.naver.com/place/1751652203</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3086,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>유네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>luvu1016@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3095,12 +3099,12 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가A동 223호 COCO.NAIL</t>
+          <t>인천광역시 서구 크리스탈로 78 엘림아트센터 304호 일부호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coco.nail_._?igsh=MXIydzZsZ2M3eGVmZw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/yu_nail_salon</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,13 +3139,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3154,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1165395528</t>
+          <t>2051656387</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165395528</t>
+          <t>https://m.place.naver.com/place/2051656387</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3172,29 +3176,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>딩가네일스튜디오</t>
+          <t>의미를 그리다</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yejiiik@naver.com</t>
+          <t>yunjbutton@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1327-6084</t>
+          <t>0507-1349-2389</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 210호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스오피스텔 상가 A동 1층 상가안쪽</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dinga_nail</t>
+          <t>http://www.instagram.com/draw_meaning_nail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3229,13 +3233,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="R30" t="n">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3248,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1879647738</t>
+          <t>1285622660</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1879647738</t>
+          <t>https://m.place.naver.com/place/1285622660</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3266,34 +3270,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>로미네일</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0rominail0@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1443-7127</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 1층 091호</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ro.mi_nail</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3314,7 +3318,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3323,13 +3327,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="R31" t="n">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3342,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2072431299</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072431299</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3360,34 +3364,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>디오뜨네일 청라본점</t>
+          <t>네일하롱</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>younge_dailylife@naver.com</t>
+          <t>mimmmm95_@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1363-3686</t>
+          <t>0507-1438-1442</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 1층 138호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KBxhGn</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3408,7 +3412,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3417,13 +3421,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>207</v>
+        <v>536</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="R32" t="n">
-        <v>216</v>
+        <v>572</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3436,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1228012496</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228012496</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3458,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>굳띵네일</t>
+          <t>쏘네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hahahaam@naver.com</t>
+          <t>choseohyun041019@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>070-4247-1016</t>
+          <t>0507-1371-4660</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로163번길 12 1층</t>
+          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodthing.nail</t>
+          <t>https://www.instagram.com/_sso_shop__/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,13 +3515,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>54</v>
+        <v>834</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R33" t="n">
-        <v>66</v>
+        <v>845</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3530,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1194539605</t>
+          <t>1293272639</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194539605</t>
+          <t>https://m.place.naver.com/place/1293272639</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3548,29 +3552,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>뷰티라운지케이 네일속눈썹피부 청라가정점</t>
+          <t>제이제이네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>beautylounge-k@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1467-7707</t>
+          <t>0507-1319-1270</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 11-3 1층 뷰티라운지케이</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautyloungek</t>
+          <t>https://www.instagram.com/jj__nail___</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3605,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>257</v>
+        <v>98</v>
       </c>
       <c r="Q34" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>360</v>
+        <v>101</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1706279657</t>
+          <t>2011413114</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1706279657</t>
+          <t>https://m.place.naver.com/place/2011413114</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3642,29 +3646,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>뷰티드시엘</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>syk1007@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1448-4452</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>https://www.instagram.com/beauty_du_ciel</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3690,7 +3694,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3699,13 +3703,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>460</v>
+        <v>173</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="R35" t="n">
-        <v>485</v>
+        <v>253</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1538853353</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1538853353</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3736,34 +3740,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>디오뜨네일 청라본점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>younge_dailylife@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1375-3428</t>
+          <t>0507-1363-3686</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 138호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>http://pf.kakao.com/_KBxhGn</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3784,7 +3788,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3793,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="Q36" t="n">
         <v>9</v>
       </c>
       <c r="R36" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1228012496</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1228012496</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3830,34 +3834,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>가비앤네일</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jmoh95@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1351-4914</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XKZexj</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3878,7 +3882,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3887,13 +3891,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="Q37" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="R37" t="n">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3906,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1145821785</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145821785</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3924,34 +3928,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>쏘네일</t>
+          <t>블링뷰네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>choseohyun041019@naver.com</t>
+          <t>bv_nail@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1371-4660</t>
+          <t>0507-1350-9502</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sso_shop__/</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3972,7 +3976,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3981,13 +3985,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>834</v>
+        <v>118</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="R38" t="n">
-        <v>845</v>
+        <v>271</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1293272639</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293272639</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4018,29 +4022,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일도래쉬도</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>suging324@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1483-3118</t>
+          <t>0507-1392-1325</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 1층 117호(네일도 래쉬도)</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHFoqY2f</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4075,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>79</v>
+        <v>460</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R39" t="n">
-        <v>97</v>
+        <v>485</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4094,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1685354839</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685354839</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4112,29 +4116,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>반스뷰티&amp;네일 청라점</t>
+          <t>네일드림</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dkfma48007@naver.com</t>
+          <t>shsally0122@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1373-7577</t>
+          <t>0507-1335-1809</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
+          <t>http://instagram.com/naild_lim</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4160,7 +4164,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4169,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>198</v>
+        <v>356</v>
       </c>
       <c r="Q40" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
-        <v>295</v>
+        <v>364</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4184,17 +4188,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1751652203</t>
+          <t>1192065742</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751652203</t>
+          <t>https://m.place.naver.com/place/1192065742</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4206,29 +4210,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>봄네일</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nb98269@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1309-5732</t>
+          <t>0507-1400-8523</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 8-10 청라봄빌딩 b106호</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/bomnail_b106</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4243,7 +4247,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4263,13 +4267,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>113</v>
+        <v>337</v>
       </c>
       <c r="Q41" t="n">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="R41" t="n">
-        <v>168</v>
+        <v>453</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,17 +4282,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1235537458</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235537458</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4300,29 +4304,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>네일할일 청라본점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>nailart1227@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1337-0812</t>
+          <t>0507-1385-4415</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 보석로18번안길 20 102호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>https://www.instagram.com/cheongna_nail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4348,7 +4352,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4357,13 +4361,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>301</v>
+        <v>46</v>
       </c>
       <c r="Q42" t="n">
-        <v>68</v>
+        <v>463</v>
       </c>
       <c r="R42" t="n">
-        <v>369</v>
+        <v>509</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4376,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>1006118353</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/1006118353</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4394,34 +4398,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>보라네일</t>
+          <t>네일리움</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>00bora00@naver.com</t>
+          <t>nuy00@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1494-0141</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로138번길 10 1층</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌 더 테라스</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bora_nail__</t>
+          <t>http://pf.kakao.com/_JwDwK</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4451,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>204</v>
+        <v>17</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4466,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>37700904</t>
+          <t>1320367719</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37700904</t>
+          <t>https://m.place.naver.com/place/1320367719</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4488,29 +4488,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일,맑음</t>
+          <t>네일도래쉬도</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sh2066@naver.com</t>
+          <t>suging324@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1350-4484</t>
+          <t>0507-1483-3118</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 6-8 1층 네일,맑음</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 1층 117호(네일도 래쉬도)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_NxlhEn</t>
+          <t>https://open.kakao.com/o/sHFoqY2f</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R44" t="n">
-        <v>320</v>
+        <v>97</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1051767791</t>
+          <t>1685354839</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051767791</t>
+          <t>https://m.place.naver.com/place/1685354839</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4582,29 +4582,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뷰티드시엘</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jysjysyessle@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1448-4452</t>
+          <t>0507-1325-3255</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_du_ciel</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4639,13 +4639,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>173</v>
+        <v>622</v>
       </c>
       <c r="Q45" t="n">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="R45" t="n">
-        <v>253</v>
+        <v>861</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4654,17 +4654,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1538853353</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538853353</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4676,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>네일퐁</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>bae_tamine@naver.com</t>
+          <t>aksk1313@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1315-1372</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 푸른로8번안길 4 1층 일부호(103호)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>https://www.instagram.com/_nailpong</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4724,7 +4724,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>353</v>
+        <v>135</v>
       </c>
       <c r="Q46" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>430</v>
+        <v>136</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>2035104802</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/2035104802</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4770,29 +4770,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>미미무드네일</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1379-2451</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 지하1층 B동 111호 미미무드네일</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_NpBeG/chat</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>154</v>
+        <v>301</v>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="R47" t="n">
-        <v>195</v>
+        <v>369</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4842,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1587592784</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587592784</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4864,34 +4864,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>미미무드네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1344-1735</t>
+          <t>0507-1379-2451</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 지하1층 B동 111호 미미무드네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>https://pf.kakao.com/_NpBeG/chat</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4912,7 +4912,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="R48" t="n">
-        <v>288</v>
+        <v>195</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4936,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>1587592784</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/1587592784</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4958,34 +4958,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일소소</t>
+          <t>오늘의기분 네일 청라본점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>rkswlwoddl84@naver.com</t>
+          <t>bae_tamine@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1415-2417</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_so_so</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5006,7 +5006,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="R49" t="n">
-        <v>291</v>
+        <v>430</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5030,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1394957062</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394957062</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5052,29 +5052,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>블링루원뷰티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>ball_11058@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1346-5358</t>
+          <t>0507-1462-3543</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5105,17 +5105,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>349</v>
+        <v>228</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="R50" t="n">
-        <v>403</v>
+        <v>237</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5124,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>1323823289</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/1323823289</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5146,29 +5146,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>르씨엘뷰티</t>
+          <t>네일서안</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0728helen@naver.com</t>
+          <t>chorong-e-@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1376-4100</t>
+          <t>0507-1367-5100</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌더테라스 상가 102동 2층 239호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://instagram.com/b_le_ciel</t>
+          <t>https://www.instagram.com/nail.seoan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5203,13 +5203,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="Q51" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="R51" t="n">
-        <v>391</v>
+        <v>335</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5218,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1826304139</t>
+          <t>1300004606</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1826304139</t>
+          <t>https://m.place.naver.com/place/1300004606</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5240,34 +5240,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일할일 청라본점</t>
+          <t>에스영이네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nailart1227@naver.com</t>
+          <t>s02nail@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1385-4415</t>
+          <t>0507-1322-9488</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 보석로18번안길 20 102호</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongna_nail</t>
+          <t>http://pf.kakao.com/_JAxdFs</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5288,7 +5288,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5297,13 +5297,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>46</v>
+        <v>428</v>
       </c>
       <c r="Q52" t="n">
-        <v>463</v>
+        <v>188</v>
       </c>
       <c r="R52" t="n">
-        <v>509</v>
+        <v>616</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5312,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1006118353</t>
+          <t>1726483094</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006118353</t>
+          <t>https://m.place.naver.com/place/1726483094</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5334,29 +5334,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>팡네일</t>
+          <t>네일소소</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nailppang@naver.com</t>
+          <t>rkswlwoddl84@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1367-8073</t>
+          <t>0507-1415-2417</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번길 6 1층</t>
+          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pang___nail</t>
+          <t>https://www.instagram.com/nail_so_so</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5391,13 +5391,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="Q53" t="n">
         <v>20</v>
       </c>
       <c r="R53" t="n">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5406,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2066386524</t>
+          <t>1394957062</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066386524</t>
+          <t>https://m.place.naver.com/place/1394957062</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5428,34 +5428,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일,미</t>
+          <t>힝네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>specialjee@naver.com</t>
+          <t>zoe0406@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1476-4143</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로233번길 3-4 103호</t>
+          <t>인천광역시 서구 청라루비로42번길 5-5 105호 힝네일,</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ytyub</t>
+          <t>https://www.instagram.com/hing_nail/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5476,7 +5472,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5485,13 +5481,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>357</v>
+        <v>449</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="R54" t="n">
-        <v>395</v>
+        <v>460</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5496,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1645376518</t>
+          <t>1715411307</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1645376518</t>
+          <t>https://m.place.naver.com/place/1715411307</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5522,25 +5518,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>요네일</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>yunjin0313@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1375-3428</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 103호</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yo_nailshop</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>512</v>
+        <v>168</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="R55" t="n">
-        <v>545</v>
+        <v>177</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5590,17 +5590,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1271412561</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271412561</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일델루나</t>
+          <t>단감네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>eatingzzz@naver.com</t>
+          <t>sytf170@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1358-7017</t>
+          <t>0507-1374-8432</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_delluna</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1534</v>
+        <v>207</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>337</v>
       </c>
       <c r="R56" t="n">
-        <v>1549</v>
+        <v>544</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5684,17 +5684,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1852644091</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852644091</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5706,29 +5706,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>푸스케어 청라점</t>
+          <t>제이네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>miwha2000@naver.com</t>
+          <t>morningapple6@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1305-8118</t>
+          <t>0507-1386-7822</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 76 1층 130호 FUSSCARE</t>
+          <t>인천광역시 서구 청라에메랄드로 99 B동 1층 026호 Jnail</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miwha2000</t>
+          <t>http://www.instagram.com/j_nail21</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1900780465</t>
+          <t>1404214241</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1900780465</t>
+          <t>https://m.place.naver.com/place/1404214241</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5800,29 +5800,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>어레브네일</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>anwlro9344@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1354-5482</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anwlro9344</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>69</v>
+        <v>314</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>270</v>
       </c>
       <c r="R58" t="n">
-        <v>74</v>
+        <v>584</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5872,17 +5872,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1364434683</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364434683</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5894,29 +5894,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>쏠네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>hansol5992@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>070-7612-9500</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매5동 203호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://www.instagram.com/ssol_nail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5951,13 +5951,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>567</v>
+        <v>73</v>
       </c>
       <c r="Q59" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>700</v>
+        <v>77</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5966,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1187656534</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1187656534</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5988,29 +5988,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>딩가네일스튜디오</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>yejiiik@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1327-6084</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 210호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://www.instagram.com/dinga_nail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6045,13 +6045,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>314</v>
+        <v>186</v>
       </c>
       <c r="Q60" t="n">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c r="R60" t="n">
-        <v>580</v>
+        <v>203</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +6060,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1879647738</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1879647738</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6082,29 +6082,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
+          <t>요네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>yunjin0313@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1323-1043</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 중봉대로612번길 10 103호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>http://www.instagram.com/yo_nailshop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,13 +6135,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>91</v>
+        <v>512</v>
       </c>
       <c r="Q61" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="R61" t="n">
-        <v>140</v>
+        <v>545</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6150,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>1271412561</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/1271412561</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6176,34 +6172,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>미드미네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>dreaming_yjso@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1338-0068</t>
+          <t>0507-1309-9513</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 청라루비로144번길 23 미드미네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>http://pf.kakao.com/_kVxoJxj</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6213,7 +6209,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6224,22 +6220,22 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>907</v>
+        <v>50</v>
       </c>
       <c r="Q62" t="n">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="R62" t="n">
-        <v>1287</v>
+        <v>70</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6244,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>1581342551</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/1581342551</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6270,34 +6266,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>네일,미</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>specialjee@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1476-4143</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 청라커낼로233번길 3-4 103호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>http://pf.kakao.com/_ytyub</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6318,7 +6314,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6327,13 +6323,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>456</v>
+        <v>357</v>
       </c>
       <c r="Q63" t="n">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="R63" t="n">
-        <v>723</v>
+        <v>395</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6338,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1645376518</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1645376518</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6364,29 +6360,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>오늘도네일도</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>nail_oneul@naver.com</t>
-        </is>
-      </c>
+          <t>네일클로버</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1449-7506</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_oneul</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6401,7 +6393,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6421,13 +6413,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>815</v>
+        <v>213</v>
       </c>
       <c r="Q64" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="R64" t="n">
-        <v>857</v>
+        <v>221</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6428,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1810678383</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810678383</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6458,29 +6450,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>askflclsrna@naver.com</t>
-        </is>
-      </c>
+          <t>와우뷰티 청라점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1323-1043</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6515,13 +6503,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>351</v>
+        <v>92</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="R65" t="n">
-        <v>362</v>
+        <v>141</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6530,17 +6518,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6552,29 +6540,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>의미를 그리다</t>
+          <t>굳띵네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yunjbutton@naver.com</t>
+          <t>hahahaam@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1349-2389</t>
+          <t>070-4247-1016</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스오피스텔 상가 A동 1층 상가안쪽</t>
+          <t>인천광역시 서구 청라에메랄드로163번길 12 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/draw_meaning_nail</t>
+          <t>https://www.instagram.com/goodthing.nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6609,13 +6597,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>264</v>
+        <v>54</v>
       </c>
       <c r="Q66" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="R66" t="n">
-        <v>343</v>
+        <v>66</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6624,17 +6612,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1285622660</t>
+          <t>1194539605</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285622660</t>
+          <t>https://m.place.naver.com/place/1194539605</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6646,25 +6634,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>유네일</t>
+          <t>네일바이윰 청라본점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>luvu1016@naver.com</t>
+          <t>db-king@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1409-8945</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로 78 엘림아트센터 304호 일부호</t>
+          <t>인천광역시 서구 청라루비로42번길 5-5 1층 101호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yu_nail_salon</t>
+          <t>https://www.instagram.com/nail_by.yoom</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6699,13 +6691,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,17 +6706,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2051656387</t>
+          <t>1031692471</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051656387</t>
+          <t>https://m.place.naver.com/place/1031692471</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6736,29 +6728,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일글로우</t>
+          <t>트윈스네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>cottonpp@naver.com</t>
+          <t>form2030@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1460-8342</t>
+          <t>0507-1309-9545</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 122호 트윈스네일</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/form2030</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6773,7 +6765,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6784,7 +6776,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6793,13 +6785,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="Q68" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R68" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6808,17 +6800,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2075971036</t>
+          <t>1102751111</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075971036</t>
+          <t>https://m.place.naver.com/place/1102751111</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6830,29 +6822,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일바이윰 청라본점</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>db-king@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1409-8945</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로42번길 5-5 1층 101호</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by.yoom</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6867,7 +6859,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6883,17 +6875,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>156</v>
+        <v>907</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>380</v>
       </c>
       <c r="R69" t="n">
-        <v>158</v>
+        <v>1287</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6902,17 +6894,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1031692471</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031692471</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6924,29 +6916,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일을기억해</t>
+          <t>뷰티라운지케이 네일속눈썹피부 청라가정점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>rimo0904@naver.com</t>
+          <t>beautylounge-k@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1491-7279</t>
+          <t>0507-1467-7707</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+          <t>인천광역시 서구 염곡로498번안길 11-3 1층 뷰티라운지케이</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/remember._nails</t>
+          <t>https://www.instagram.com/beautyloungek</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6972,7 +6964,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6981,13 +6973,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="R70" t="n">
-        <v>254</v>
+        <v>360</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6996,17 +6988,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1811328950</t>
+          <t>1706279657</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811328950</t>
+          <t>https://m.place.naver.com/place/1706279657</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7018,34 +7010,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일또온나 청라점</t>
+          <t>마이즈네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2xmania2xj@naver.com</t>
+          <t>flyue@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1338-3150</t>
+          <t>0507-1417-2584</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+          <t>인천광역시 서구 청라루비로144번길 19 . 1층 마이즈네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_tto_onna</t>
+          <t>https://pf.kakao.com/_BMRfG</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7066,7 +7058,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7075,13 +7067,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>247</v>
+        <v>180</v>
       </c>
       <c r="Q71" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>310</v>
+        <v>184</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7090,17 +7082,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1546215593</t>
+          <t>1176695071</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546215593</t>
+          <t>https://m.place.naver.com/place/1176695071</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7112,29 +7104,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일드림</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>shsally0122@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1335-1809</t>
+          <t>0507-1408-0807</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://instagram.com/naild_lim</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7169,13 +7161,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>356</v>
+        <v>610</v>
       </c>
       <c r="Q72" t="n">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="R72" t="n">
-        <v>364</v>
+        <v>828</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7184,17 +7176,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1192065742</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192065742</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7206,29 +7198,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아지트밍</t>
+          <t>네일또온나 청라점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>suni_hh@naver.com</t>
+          <t>2xmania2xj@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1492-7763</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 지하1층 B101-1호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/suni_hh</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7243,7 +7235,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7263,13 +7255,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>434</v>
+        <v>247</v>
       </c>
       <c r="Q73" t="n">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="R73" t="n">
-        <v>552</v>
+        <v>310</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7278,17 +7270,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1742689242</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742689242</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7357,13 +7349,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q74" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R74" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7382,7 +7374,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7394,34 +7386,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>제이제이네일</t>
+          <t>츄네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>chuu_nail@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1319-1270</t>
+          <t>0507-1355-7059</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 103동 211호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jj__nail___</t>
+          <t>http://pf.kakao.com/_DyBJs</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7442,7 +7434,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7451,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7466,17 +7458,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2011413114</t>
+          <t>1673851812</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011413114</t>
+          <t>https://m.place.naver.com/place/1673851812</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7488,29 +7480,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일하롱</t>
+          <t>네일델루나</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mimmmm95_@naver.com</t>
+          <t>eatingzzz@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1438-1442</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7545,13 +7537,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>536</v>
+        <v>1534</v>
       </c>
       <c r="Q76" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="R76" t="n">
-        <v>572</v>
+        <v>1549</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7560,17 +7552,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/청라_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/청라_네일샵.xlsx
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>보라네일</t>
+          <t>이르미네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00bora00@naver.com</t>
+          <t>aboutdanchuu@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1494-0141</t>
+          <t>0507-1391-3129</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로138번길 10 1층</t>
+          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bora_nail__</t>
+          <t>http://pf.kakao.com/_ezxgrG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="R2" t="n">
-        <v>204</v>
+        <v>342</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37700904</t>
+          <t>1596414337</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37700904</t>
+          <t>https://m.place.naver.com/place/1596414337</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>오늘의 네일</t>
+          <t>굳띵네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>redcherry88@naver.com</t>
+          <t>hahahaam@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1484-2578</t>
+          <t>070-4247-1016</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 담지로8번길 7-10 1층</t>
+          <t>인천광역시 서구 청라에메랄드로163번길 12 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/0neulnail</t>
+          <t>https://www.instagram.com/goodthing.nail</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1312212877</t>
+          <t>1194539605</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1312212877</t>
+          <t>https://m.place.naver.com/place/1194539605</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,30 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>민블리네일</t>
+          <t>미드미네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eun301010_@naver.com</t>
+          <t>dreaming_yjso@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1309-9513</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-8 . 1층 109호</t>
+          <t>인천광역시 서구 청라루비로144번길 23 미드미네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_thelove?igsh=MTloYm44ZHd2OHZmdw%3D%3D&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_kVxoJxj</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1370458509</t>
+          <t>1581342551</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370458509</t>
+          <t>https://m.place.naver.com/place/1581342551</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일을기억해</t>
+          <t>쏘네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rimo0904@naver.com</t>
+          <t>choseohyun041019@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1491-7279</t>
+          <t>0507-1371-4660</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
+          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/remember._nails</t>
+          <t>https://www.instagram.com/_sso_shop__/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>210</v>
+        <v>834</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>254</v>
+        <v>845</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1811328950</t>
+          <t>1293272639</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811328950</t>
+          <t>https://m.place.naver.com/place/1293272639</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -936,25 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>온더네일 앤 스킨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>sing1228@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1444-7836</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가A동 223호 COCO.NAIL</t>
+          <t>인천광역시 서구 가정로 437 SK리더스뷰 301동 302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coco.nail_._?igsh=MXIydzZsZ2M3eGVmZw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/on_the_nail302</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1165395528</t>
+          <t>1782633744</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165395528</t>
+          <t>https://m.place.naver.com/place/1782633744</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인생네일 청라본점</t>
+          <t>네일위드유 문제성발톱 속눈썹</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>askflclsrna@naver.com</t>
+          <t>nail_with_yoo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1301-5228</t>
+          <t>0507-1344-1735</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/life_nail_salon</t>
+          <t>https://www.instagram.com/nail_with_yoo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>362</v>
+        <v>288</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1764464663</t>
+          <t>1776289071</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1764464663</t>
+          <t>https://m.place.naver.com/place/1776289071</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일글로우</t>
+          <t>네일하롱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cottonpp@naver.com</t>
+          <t>mimmmm95_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1460-8342</t>
+          <t>0507-1438-1442</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail._.harong</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>64</v>
+        <v>536</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="R8" t="n">
-        <v>120</v>
+        <v>572</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2075971036</t>
+          <t>1264211104</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075971036</t>
+          <t>https://m.place.naver.com/place/1264211104</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이언니네 청라본점</t>
+          <t>오늘의기분 네일 청라본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mina20624@naver.com</t>
+          <t>bae_tamine@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1332-6316</t>
+          <t>0507-1307-8929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
+          <t>http://pf.kakao.com/_pxcsgb</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1262,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1271,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>665</v>
+        <v>353</v>
       </c>
       <c r="Q9" t="n">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="R9" t="n">
-        <v>832</v>
+        <v>430</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1095756447</t>
+          <t>1747055394</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1095756447</t>
+          <t>https://m.place.naver.com/place/1747055394</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>섬세하나네일 청라본점</t>
+          <t>네일바이윰 청라본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sumsehana@naver.com</t>
+          <t>db-king@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1481-0788</t>
+          <t>0507-1409-8945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
+          <t>인천광역시 서구 청라루비로42번길 5-5 1층 101호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sumsehana</t>
+          <t>https://www.instagram.com/nail_by.yoom</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>620</v>
+        <v>156</v>
       </c>
       <c r="Q10" t="n">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>751</v>
+        <v>158</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1251340543</t>
+          <t>1031692471</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251340543</t>
+          <t>https://m.place.naver.com/place/1031692471</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일, 안느</t>
+          <t>네일퐁</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gkswngml3594@naver.com</t>
+          <t>aksk1313@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1403-9410</t>
+          <t>0507-1315-1372</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로7번길 14 1층 102호</t>
+          <t>인천광역시 서구 푸른로8번안길 4 1층 일부호(103호)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/0n_anne</t>
+          <t>https://www.instagram.com/_nailpong</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1256153031</t>
+          <t>2035104802</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256153031</t>
+          <t>https://m.place.naver.com/place/2035104802</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1496,34 +1504,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>가비앤네일</t>
+          <t>프롬쥬네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jmoh95@naver.com</t>
+          <t>dlaalswn89@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1351-4914</t>
+          <t>0507-1327-0666</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
+          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XKZexj</t>
+          <t>https://blog.naver.com/dlaalswn89</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1533,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1544,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1553,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>301</v>
+        <v>567</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="R12" t="n">
-        <v>332</v>
+        <v>700</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1145821785</t>
+          <t>1545913000</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145821785</t>
+          <t>https://m.place.naver.com/place/1545913000</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>봄네일</t>
+          <t>어레브네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nb98269@naver.com</t>
+          <t>anwlro9344@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1309-5732</t>
+          <t>0507-1354-5482</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 8-10 청라봄빌딩 b106호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://instagram.com/bomnail_b106</t>
+          <t>https://blog.naver.com/anwlro9344</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="Q13" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1235537458</t>
+          <t>1364434683</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235537458</t>
+          <t>https://m.place.naver.com/place/1364434683</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>프롬쥬네일</t>
+          <t>감성네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dlaalswn89@naver.com</t>
+          <t>gamseongnail@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1327-0666</t>
+          <t>0507-1424-4545</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 1F, b동 106호 프롬쥬네일</t>
+          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlaalswn89</t>
+          <t>https://www.instagram.com/gam_seongnail/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>567</v>
+        <v>452</v>
       </c>
       <c r="Q14" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="R14" t="n">
-        <v>700</v>
+        <v>617</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1545913000</t>
+          <t>1382824710</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545913000</t>
+          <t>https://m.place.naver.com/place/1382824710</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아지트밍</t>
+          <t>제이언니네 청라본점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>suni_hh@naver.com</t>
+          <t>mina20624@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1492-7763</t>
+          <t>0507-1332-6316</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 지하1층 B101-1호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커넬웨이 216호 제이언니네 인천청라점</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/suni_hh</t>
+          <t>https://youtube.com/channel/UCv_8eMMQzuhisKAivnHGdTQ</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>434</v>
+        <v>666</v>
       </c>
       <c r="Q15" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="R15" t="n">
-        <v>552</v>
+        <v>833</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1858,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1742689242</t>
+          <t>1095756447</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742689242</t>
+          <t>https://m.place.naver.com/place/1095756447</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1872,34 +1880,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일,맑음</t>
+          <t>네일달다 청라점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sh2066@naver.com</t>
+          <t>haru_log_in@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1350-4484</t>
+          <t>0507-1325-3255</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 6-8 1층 네일,맑음</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_NxlhEn</t>
+          <t>http://instagram.com/naildalda_</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1920,7 +1928,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>300</v>
+        <v>625</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="R16" t="n">
-        <v>320</v>
+        <v>866</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1952,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1051767791</t>
+          <t>1040857451</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051767791</t>
+          <t>https://m.place.naver.com/place/1040857451</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1974,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일위드유 문제성발톱 속눈썹</t>
+          <t>네일그리미</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nail_with_yoo@naver.com</t>
+          <t>tory0413@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1344-1735</t>
+          <t>0507-1346-5358</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 2층 215호</t>
+          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_with_yoo</t>
+          <t>https://www.instagram.com/nail.grimmy</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2023,13 +2031,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="R17" t="n">
-        <v>288</v>
+        <v>403</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2046,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1776289071</t>
+          <t>1125220368</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776289071</t>
+          <t>https://m.place.naver.com/place/1125220368</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2060,34 +2068,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>푸스케어 청라점</t>
+          <t>블링뷰네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>miwha2000@naver.com</t>
+          <t>bv_nail@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1305-8118</t>
+          <t>0507-1350-9502</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 76 1층 130호 FUSSCARE</t>
+          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miwha2000</t>
+          <t>http://pf.kakao.com/_RqUxcG</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2097,7 +2105,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2108,7 +2116,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q18" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="R18" t="n">
-        <v>222</v>
+        <v>271</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2140,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1900780465</t>
+          <t>1259415075</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1900780465</t>
+          <t>https://m.place.naver.com/place/1259415075</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2162,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>로미네일</t>
+          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0rominail0@naver.com</t>
+          <t>01192291122@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1443-7127</t>
+          <t>0507-1338-0068</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 1층 091호</t>
+          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ro.mi_nail</t>
+          <t>https://blog.naver.com/01192291122</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2191,7 +2199,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2207,17 +2215,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>78</v>
+        <v>907</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="R19" t="n">
-        <v>78</v>
+        <v>1287</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2234,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2072431299</t>
+          <t>1868333219</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072431299</t>
+          <t>https://m.place.naver.com/place/1868333219</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2248,30 +2256,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일에딧</t>
+          <t>소월네일 청라점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>byddooroo@naver.com</t>
+          <t>66cjstk@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1433-8310</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
+          <t>인천광역시 서구 청라루비로 99 대우메디피아 1층 101호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_dZxhxcn</t>
+          <t>https://blog.naver.com/66cjstk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2281,7 +2293,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2292,7 +2304,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2301,13 +2313,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>801</v>
+        <v>27</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="R20" t="n">
-        <v>807</v>
+        <v>84</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2328,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2041818773</t>
+          <t>1477188152</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041818773</t>
+          <t>https://m.place.naver.com/place/1477188152</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2338,34 +2350,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>르씨엘뷰티</t>
+          <t>뷰티드시엘</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0728helen@naver.com</t>
+          <t>syk1007@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1376-4100</t>
+          <t>0507-1448-4452</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌더테라스 상가 102동 2층 239호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://instagram.com/b_le_ciel</t>
+          <t>https://www.instagram.com/beauty_du_ciel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2375,7 +2387,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2395,13 +2407,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="Q21" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="R21" t="n">
-        <v>391</v>
+        <v>257</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2422,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1826304139</t>
+          <t>1538853353</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1826304139</t>
+          <t>https://m.place.naver.com/place/1538853353</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2444,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>네일할일 청라본점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mobi04@naver.com</t>
+          <t>nailart1227@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1398-8291</t>
+          <t>0507-1385-4415</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
+          <t>인천광역시 서구 보석로18번안길 20 102호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_kkomkkom/</t>
+          <t>https://www.instagram.com/cheongna_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2489,13 +2501,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>573</v>
+        <v>46</v>
       </c>
       <c r="Q22" t="n">
-        <v>846</v>
+        <v>463</v>
       </c>
       <c r="R22" t="n">
-        <v>1419</v>
+        <v>509</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2516,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1090442730</t>
+          <t>1006118353</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1090442730</t>
+          <t>https://m.place.naver.com/place/1006118353</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2526,29 +2538,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1248네일</t>
+          <t>트윈스네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1248nail@naver.com</t>
+          <t>form2030@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1479-8978</t>
+          <t>0507-1309-9545</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 122호 트윈스네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1248_nail</t>
+          <t>https://blog.naver.com/form2030</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2563,7 +2575,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2574,7 +2586,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2595,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>457</v>
+        <v>105</v>
       </c>
       <c r="Q23" t="n">
-        <v>267</v>
+        <v>27</v>
       </c>
       <c r="R23" t="n">
-        <v>724</v>
+        <v>132</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2610,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1537239618</t>
+          <t>1102751111</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537239618</t>
+          <t>https://m.place.naver.com/place/1102751111</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2620,25 +2632,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>도르네일</t>
+          <t>에스영이네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bnm4818@naver.com</t>
+          <t>s02nail@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1322-9488</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/hCmFKNexK</t>
+          <t>http://pf.kakao.com/_JAxdFs</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2648,7 +2664,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2664,7 +2680,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2673,13 +2689,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>728</v>
+        <v>428</v>
       </c>
       <c r="Q24" t="n">
-        <v>54</v>
+        <v>188</v>
       </c>
       <c r="R24" t="n">
-        <v>782</v>
+        <v>616</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2704,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1001824596</t>
+          <t>1726483094</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1001824596</t>
+          <t>https://m.place.naver.com/place/1726483094</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2726,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오늘도네일도</t>
+          <t>딩가네일스튜디오</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nail_oneul@naver.com</t>
+          <t>yejiiik@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1449-7506</t>
+          <t>0507-1327-6084</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 210호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_oneul</t>
+          <t>https://www.instagram.com/dinga_nail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2747,7 +2763,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2767,13 +2783,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>815</v>
+        <v>186</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="R25" t="n">
-        <v>857</v>
+        <v>203</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2798,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1810678383</t>
+          <t>1879647738</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810678383</t>
+          <t>https://m.place.naver.com/place/1879647738</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2820,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>어레브네일</t>
+          <t>봄네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>anwlro9344@naver.com</t>
+          <t>nb98269@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1354-5482</t>
+          <t>0507-1309-5732</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동 202호</t>
+          <t>인천광역시 서구 청라커낼로288번길 8-10 청라봄빌딩 b106호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anwlro9344</t>
+          <t>http://instagram.com/bomnail_b106</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2841,7 +2857,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2861,13 +2877,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="R26" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2892,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1364434683</t>
+          <t>1235537458</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364434683</t>
+          <t>https://m.place.naver.com/place/1235537458</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2914,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>팡네일</t>
+          <t>1248네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nailppang@naver.com</t>
+          <t>1248nail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1367-8073</t>
+          <t>0507-1479-8978</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번길 6 1층</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스 C동 205호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pang___nail</t>
+          <t>https://www.instagram.com/1248_nail</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2955,13 +2971,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="R27" t="n">
-        <v>40</v>
+        <v>724</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2986,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2066386524</t>
+          <t>1537239618</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066386524</t>
+          <t>https://m.place.naver.com/place/1537239618</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -2992,29 +3008,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>반스뷰티&amp;네일 청라점</t>
+          <t>네일무디크</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dkfma48007@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1373-7577</t>
+          <t>0507-1375-3428</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
+          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
+          <t>https://www.instagram.com/nail_moodique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3040,7 +3056,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3049,13 +3065,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="Q28" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="R28" t="n">
-        <v>295</v>
+        <v>177</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3080,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1751652203</t>
+          <t>1811715033</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751652203</t>
+          <t>https://m.place.naver.com/place/1811715033</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3086,25 +3102,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>유네일</t>
+          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>luvu1016@naver.com</t>
+          <t>dlgufl0924@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1408-0807</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로 78 엘림아트센터 304호 일부호</t>
+          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yu_nail_salon</t>
+          <t>https://www.instagram.com/lantienail_official/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3139,13 +3159,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>14</v>
+        <v>610</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>218</v>
       </c>
       <c r="R29" t="n">
-        <v>15</v>
+        <v>828</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3174,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2051656387</t>
+          <t>37922472</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051656387</t>
+          <t>https://m.place.naver.com/place/37922472</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3176,29 +3196,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>의미를 그리다</t>
+          <t>아이퀸네일 청라점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yunjbutton@naver.com</t>
+          <t>gamejaki@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1349-2389</t>
+          <t>0507-1351-6212</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스오피스텔 상가 A동 1층 상가안쪽</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/draw_meaning_nail</t>
+          <t>https://www.instagram.com/iqueen_nail.cn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3233,13 +3253,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>264</v>
+        <v>314</v>
       </c>
       <c r="Q30" t="n">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="R30" t="n">
-        <v>343</v>
+        <v>600</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,17 +3268,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1285622660</t>
+          <t>1330577008</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285622660</t>
+          <t>https://m.place.naver.com/place/1330577008</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3270,34 +3290,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이르미네일</t>
+          <t>푸스케어 청라점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>aboutdanchuu@naver.com</t>
+          <t>miwha2000@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1391-3129</t>
+          <t>0507-1305-8118</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 124 디오스텔 1F 124호 CU편의점 바로 옆</t>
+          <t>인천광역시 서구 청라루비로 76 1층 130호 FUSSCARE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ezxgrG</t>
+          <t>https://blog.naver.com/miwha2000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3307,7 +3327,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3318,7 +3338,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3327,13 +3347,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="Q31" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R31" t="n">
-        <v>342</v>
+        <v>222</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,17 +3362,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1596414337</t>
+          <t>1900780465</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596414337</t>
+          <t>https://m.place.naver.com/place/1900780465</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3364,29 +3384,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일하롱</t>
+          <t>네일소소</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mimmmm95_@naver.com</t>
+          <t>rkswlwoddl84@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1438-1442</t>
+          <t>0507-1415-2417</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 1층 101호</t>
+          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.harong</t>
+          <t>https://www.instagram.com/nail_so_so</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3421,13 +3441,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>536</v>
+        <v>271</v>
       </c>
       <c r="Q32" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
-        <v>572</v>
+        <v>291</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3436,17 +3456,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1264211104</t>
+          <t>1394957062</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264211104</t>
+          <t>https://m.place.naver.com/place/1394957062</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3458,29 +3478,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>쏘네일</t>
+          <t>힝네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>choseohyun041019@naver.com</t>
+          <t>zoe0406@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1371-4660</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 90 2층 쏘네일</t>
+          <t>인천광역시 서구 청라루비로42번길 5-5 105호 힝네일,</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sso_shop__/</t>
+          <t>https://www.instagram.com/hing_nail/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3515,13 +3531,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>834</v>
+        <v>449</v>
       </c>
       <c r="Q33" t="n">
         <v>11</v>
       </c>
       <c r="R33" t="n">
-        <v>845</v>
+        <v>460</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,17 +3546,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1293272639</t>
+          <t>1715411307</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293272639</t>
+          <t>https://m.place.naver.com/place/1715411307</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3552,29 +3568,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>제이제이네일</t>
+          <t>네일을기억해</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>yang4550@naver.com</t>
+          <t>rimo0904@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1319-1270</t>
+          <t>0507-1491-7279</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-15 4층 위드유스페이스 411호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jj__nail___</t>
+          <t>https://www.instagram.com/remember._nails</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3600,7 +3616,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3609,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>98</v>
+        <v>211</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="R34" t="n">
-        <v>101</v>
+        <v>255</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3640,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2011413114</t>
+          <t>1811328950</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2011413114</t>
+          <t>https://m.place.naver.com/place/1811328950</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3646,29 +3662,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>뷰티드시엘</t>
+          <t>섬세하나네일 청라본점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>syk1007@naver.com</t>
+          <t>sumsehana@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1448-4452</t>
+          <t>0507-1481-0788</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 221 일부호</t>
+          <t>인천광역시 서구 청라루비로 95 경연프라자 2층 201호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_du_ciel</t>
+          <t>https://blog.naver.com/sumsehana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3683,7 +3699,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3703,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>173</v>
+        <v>621</v>
       </c>
       <c r="Q35" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="R35" t="n">
-        <v>253</v>
+        <v>752</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,17 +3734,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1538853353</t>
+          <t>1251340543</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538853353</t>
+          <t>https://m.place.naver.com/place/1251340543</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3740,34 +3756,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>디오뜨네일 청라본점</t>
+          <t>네일또온나 청라점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>younge_dailylife@naver.com</t>
+          <t>2xmania2xj@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1363-3686</t>
+          <t>0507-1338-3150</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 1층 138호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KBxhGn</t>
+          <t>https://www.instagram.com/nail_tto_onna</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3788,7 +3804,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3797,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="R36" t="n">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,17 +3828,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1228012496</t>
+          <t>1546215593</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228012496</t>
+          <t>https://m.place.naver.com/place/1546215593</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3834,29 +3850,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일그리미</t>
+          <t>와우뷰티 청라점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>tory0413@naver.com</t>
+          <t>e5174@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1346-5358</t>
+          <t>0507-1323-1043</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 131 상가3동 112호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.grimmy</t>
+          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3891,13 +3907,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>349</v>
+        <v>92</v>
       </c>
       <c r="Q37" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="R37" t="n">
-        <v>403</v>
+        <v>141</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,17 +3922,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1125220368</t>
+          <t>1012993987</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125220368</t>
+          <t>https://m.place.naver.com/place/1012993987</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -3928,34 +3944,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>블링뷰네일</t>
+          <t>네일델루나</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bv_nail@naver.com</t>
+          <t>eatingzzz@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1350-9502</t>
+          <t>0507-1358-7017</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 동문뒷편상가 1층 [루원시티대성베르힐]</t>
+          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_RqUxcG</t>
+          <t>http://instagram.com/nail_delluna</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3976,7 +3992,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3985,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>118</v>
+        <v>1536</v>
       </c>
       <c r="Q38" t="n">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="R38" t="n">
-        <v>271</v>
+        <v>1551</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,17 +4016,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1259415075</t>
+          <t>1852644091</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259415075</t>
+          <t>https://m.place.naver.com/place/1852644091</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4022,34 +4038,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>라나뷰티 청라본점</t>
+          <t>미미무드네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>yellowground_@naver.com</t>
+          <t>findmyperfectdays@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1392-1325</t>
+          <t>0507-1379-2451</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 지하1층 B동 111호 미미무드네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_rananail</t>
+          <t>https://pf.kakao.com/_NpBeG/chat</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4079,13 +4095,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>460</v>
+        <v>154</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="R39" t="n">
-        <v>485</v>
+        <v>195</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,17 +4110,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1071013615</t>
+          <t>1587592784</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071013615</t>
+          <t>https://m.place.naver.com/place/1587592784</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4116,29 +4132,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일드림</t>
+          <t>네일도래쉬도</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shsally0122@naver.com</t>
+          <t>suging324@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1335-1809</t>
+          <t>0507-1483-3118</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 1층 117호(네일도 래쉬도)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://instagram.com/naild_lim</t>
+          <t>https://open.kakao.com/o/sHFoqY2f</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4164,7 +4180,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4173,13 +4189,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="R40" t="n">
-        <v>364</v>
+        <v>97</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,17 +4204,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1192065742</t>
+          <t>1685354839</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192065742</t>
+          <t>https://m.place.naver.com/place/1685354839</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4210,29 +4226,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>포네하네일</t>
+          <t>르씨엘뷰티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>forestnh@naver.com</t>
+          <t>0728helen@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1400-8523</t>
+          <t>0507-1376-4100</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌더테라스 상가 102동 2층 239호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/forestnh</t>
+          <t>http://instagram.com/b_le_ciel</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,7 +4263,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4267,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="Q41" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="R41" t="n">
-        <v>453</v>
+        <v>391</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,17 +4298,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1672609930</t>
+          <t>1826304139</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672609930</t>
+          <t>https://m.place.naver.com/place/1826304139</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4304,29 +4320,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일할일 청라본점</t>
+          <t>네일서안</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>nailart1227@naver.com</t>
+          <t>chorong-e-@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1385-4415</t>
+          <t>0507-1367-5100</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 보석로18번안길 20 102호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongna_nail</t>
+          <t>https://www.instagram.com/nail.seoan</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4361,13 +4377,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>46</v>
+        <v>314</v>
       </c>
       <c r="Q42" t="n">
-        <v>463</v>
+        <v>22</v>
       </c>
       <c r="R42" t="n">
-        <v>509</v>
+        <v>336</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,17 +4392,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1006118353</t>
+          <t>1300004606</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006118353</t>
+          <t>https://m.place.naver.com/place/1300004606</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4398,30 +4414,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일리움</t>
+          <t>단감네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nuy00@naver.com</t>
+          <t>aayoon7@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1374-8432</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌 더 테라스</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JwDwK</t>
+          <t>https://www.instagram.com/dangam_nail/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4442,7 +4462,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4451,13 +4471,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>337</v>
       </c>
       <c r="R43" t="n">
-        <v>17</v>
+        <v>544</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4486,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1320367719</t>
+          <t>1985862694</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320367719</t>
+          <t>https://m.place.naver.com/place/1985862694</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4488,34 +4508,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일도래쉬도</t>
+          <t>오늘도네일도</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>suging324@naver.com</t>
+          <t>nail_oneul@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1483-3118</t>
+          <t>0507-1449-7506</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 1층 117호(네일도 래쉬도)</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 235호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sHFoqY2f</t>
+          <t>https://blog.naver.com/nail_oneul</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4525,7 +4545,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4536,7 +4556,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4545,13 +4565,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>79</v>
+        <v>818</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
-        <v>97</v>
+        <v>860</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4560,17 +4580,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1685354839</t>
+          <t>1810678383</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685354839</t>
+          <t>https://m.place.naver.com/place/1810678383</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4582,29 +4602,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일달다 청라점</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>haru_log_in@naver.com</t>
+          <t>mobi04@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1325-3255</t>
+          <t>0507-1398-8291</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 디오스텔오피스텔 207호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 한신더휴커낼웨이 151호 꼼꼼네일</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/naildalda_</t>
+          <t>https://www.instagram.com/nail_kkomkkom/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4639,13 +4659,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>622</v>
+        <v>573</v>
       </c>
       <c r="Q45" t="n">
-        <v>239</v>
+        <v>849</v>
       </c>
       <c r="R45" t="n">
-        <v>861</v>
+        <v>1422</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4654,17 +4674,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1040857451</t>
+          <t>1090442730</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040857451</t>
+          <t>https://m.place.naver.com/place/1090442730</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4676,29 +4696,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일퐁</t>
+          <t>보라네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>aksk1313@naver.com</t>
+          <t>00bora00@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1315-1372</t>
+          <t>0507-1494-0141</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로8번안길 4 1층 일부호(103호)</t>
+          <t>인천광역시 서구 청라라임로138번길 10 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nailpong</t>
+          <t>https://www.instagram.com/bora_nail__</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4724,7 +4744,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4733,13 +4753,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4768,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2035104802</t>
+          <t>37700904</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035104802</t>
+          <t>https://m.place.naver.com/place/37700904</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4770,29 +4790,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>레푸스 청라점</t>
+          <t>네일,미</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dldeoqkr@naver.com</t>
+          <t>specialjee@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1337-0812</t>
+          <t>0507-1476-4143</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
+          <t>인천광역시 서구 청라커낼로233번길 3-4 103호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYKKOFJe</t>
+          <t>http://pf.kakao.com/_ytyub</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4827,13 +4847,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>301</v>
+        <v>357</v>
       </c>
       <c r="Q47" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="R47" t="n">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4862,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1742485791</t>
+          <t>1645376518</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742485791</t>
+          <t>https://m.place.naver.com/place/1645376518</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4864,29 +4884,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>미미무드네일</t>
+          <t>마이즈네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>findmyperfectdays@naver.com</t>
+          <t>flyue@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1379-2451</t>
+          <t>0507-1417-2584</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 지하1층 B동 111호 미미무드네일</t>
+          <t>인천광역시 서구 청라루비로144번길 19 . 1층 마이즈네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_NpBeG/chat</t>
+          <t>https://pf.kakao.com/_BMRfG</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4921,13 +4941,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4956,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1587592784</t>
+          <t>1176695071</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587592784</t>
+          <t>https://m.place.naver.com/place/1176695071</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -4958,29 +4978,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>오늘의기분 네일 청라본점</t>
+          <t>디오뜨네일 청라본점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bae_tamine@naver.com</t>
+          <t>younge_dailylife@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1307-8929</t>
+          <t>0507-1363-3686</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 린스트라우스 상가a동 116호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 1층 138호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pxcsgb</t>
+          <t>http://pf.kakao.com/_KBxhGn</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5015,13 +5035,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>353</v>
+        <v>208</v>
       </c>
       <c r="Q49" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="R49" t="n">
-        <v>430</v>
+        <v>217</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5050,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1747055394</t>
+          <t>1228012496</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747055394</t>
+          <t>https://m.place.naver.com/place/1228012496</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5052,29 +5072,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>블링루원뷰티</t>
+          <t>의미를 그리다</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ball_11058@naver.com</t>
+          <t>yunjbutton@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1462-3543</t>
+          <t>0507-1349-2389</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
+          <t>인천광역시 서구 청라라임로 85 린스트라우스오피스텔 상가 A동 1층 상가안쪽</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/draw_meaning_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5084,7 +5104,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5105,17 +5125,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="R50" t="n">
-        <v>237</v>
+        <v>343</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5144,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1323823289</t>
+          <t>1285622660</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1323823289</t>
+          <t>https://m.place.naver.com/place/1285622660</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5146,34 +5166,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일서안</t>
+          <t>가비앤네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>chorong-e-@naver.com</t>
+          <t>rlawogusaks@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1367-5100</t>
+          <t>0507-1351-4914</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 . 1층 C07호 네일서안 (청라동)</t>
+          <t>인천광역시 서구 청라라임로 100 1층 가비앤네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.seoan</t>
+          <t>http://pf.kakao.com/_XKZexj</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5194,7 +5214,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5203,13 +5223,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R51" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5238,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1300004606</t>
+          <t>1145821785</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300004606</t>
+          <t>https://m.place.naver.com/place/1145821785</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5240,29 +5260,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>에스영이네일</t>
+          <t>네일,맑음</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>s02nail@naver.com</t>
+          <t>sh2066@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1322-9488</t>
+          <t>0507-1350-4484</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 113호</t>
+          <t>인천광역시 서구 청라루비로144번길 6-8 1층 네일,맑음</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JAxdFs</t>
+          <t>https://pf.kakao.com/_NxlhEn</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5297,13 +5317,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>428</v>
+        <v>300</v>
       </c>
       <c r="Q52" t="n">
-        <v>188</v>
+        <v>20</v>
       </c>
       <c r="R52" t="n">
-        <v>616</v>
+        <v>320</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5332,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1726483094</t>
+          <t>1051767791</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726483094</t>
+          <t>https://m.place.naver.com/place/1051767791</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5334,34 +5354,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일소소</t>
+          <t>네일리움</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rkswlwoddl84@naver.com</t>
+          <t>nuy00@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1415-2417</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 지웰에스테이트 207호</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 현대썬앤빌 더 테라스</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_so_so</t>
+          <t>http://pf.kakao.com/_JwDwK</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5382,7 +5398,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5391,13 +5407,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>271</v>
+        <v>12</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>291</v>
+        <v>17</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5422,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1394957062</t>
+          <t>1320367719</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394957062</t>
+          <t>https://m.place.naver.com/place/1320367719</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5428,25 +5444,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>힝네일</t>
+          <t>라나뷰티 청라본점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>zoe0406@naver.com</t>
+          <t>yellowground_@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1392-1325</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로42번길 5-5 105호 힝네일,</t>
+          <t>인천광역시 서구 청라한내로 96 하엘에스페이스 7층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hing_nail/</t>
+          <t>https://www.instagram.com/_rananail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5472,7 +5492,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5481,13 +5501,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="R54" t="n">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5496,17 +5516,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1715411307</t>
+          <t>1071013615</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1715411307</t>
+          <t>https://m.place.naver.com/place/1071013615</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5518,29 +5538,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일무디크</t>
+          <t>반스뷰티&amp;네일 청라점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>e5174@naver.com</t>
+          <t>dkfma48007@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1375-3428</t>
+          <t>0507-1373-7577</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 25 상가 2동 106호 네일무디크</t>
+          <t>인천광역시 서구 비즈니스로 165 청라모아미래도아파트단지내상가 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_moodique</t>
+          <t>https://www.instagram.com/ban_s_beauty?igsh=cmI3djEyOXJjcGJm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5566,7 +5586,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5575,13 +5595,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="R55" t="n">
-        <v>177</v>
+        <v>293</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5590,17 +5610,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1811715033</t>
+          <t>1751652203</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811715033</t>
+          <t>https://m.place.naver.com/place/1751652203</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5612,29 +5632,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>단감네일</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sytf170@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1374-8432</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 D05호 단감네일</t>
+          <t>인천광역시 서구 청라라임로 85 상가A동 223호 COCO.NAIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dangam_nail/</t>
+          <t>https://www.instagram.com/coco.nail_._?igsh=MXIydzZsZ2M3eGVmZw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5669,13 +5685,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>207</v>
+        <v>75</v>
       </c>
       <c r="Q56" t="n">
-        <v>337</v>
+        <v>23</v>
       </c>
       <c r="R56" t="n">
-        <v>544</v>
+        <v>98</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5684,17 +5700,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1985862694</t>
+          <t>1165395528</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985862694</t>
+          <t>https://m.place.naver.com/place/1165395528</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5706,29 +5722,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>제이네일</t>
+          <t>네일글로우</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>morningapple6@naver.com</t>
+          <t>cottonpp@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1386-7822</t>
+          <t>0507-1460-8342</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 B동 1층 026호 Jnail</t>
+          <t>인천광역시 서구 염곡로498번안길 20 제이에스프라자 2층 에디뷰티랩</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/j_nail21</t>
+          <t>https://www.instagram.com/nail__glow82?igsh=eGNzODFjM2Y2djlx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5763,13 +5779,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="R57" t="n">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5778,17 +5794,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1404214241</t>
+          <t>2075971036</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404214241</t>
+          <t>https://m.place.naver.com/place/2075971036</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5800,29 +5816,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아이퀸네일 청라점</t>
+          <t>아지트밍</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gamejaki@naver.com</t>
+          <t>suni_hh@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1351-6212</t>
+          <t>0507-1492-7763</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 1층 A39호</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 A동 지하1층 B101-1호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/iqueen_nail.cn</t>
+          <t>https://blog.naver.com/suni_hh</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5837,7 +5853,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5857,13 +5873,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>314</v>
+        <v>434</v>
       </c>
       <c r="Q58" t="n">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="R58" t="n">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5872,17 +5888,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1330577008</t>
+          <t>1742689242</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330577008</t>
+          <t>https://m.place.naver.com/place/1742689242</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5894,29 +5910,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>쏠네일</t>
+          <t>뷰티라운지케이 네일속눈썹피부 청라가정점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>hansol5992@naver.com</t>
+          <t>beautylounge-k@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>070-7612-9500</t>
+          <t>0507-1467-7707</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매5동 203호</t>
+          <t>인천광역시 서구 염곡로498번안길 11-3 1층 뷰티라운지케이</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssol_nail</t>
+          <t>https://www.instagram.com/beautyloungek</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5951,13 +5967,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="R59" t="n">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5982,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1187656534</t>
+          <t>1706279657</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187656534</t>
+          <t>https://m.place.naver.com/place/1706279657</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -5988,29 +6004,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>딩가네일스튜디오</t>
+          <t>제이제이네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>yejiiik@naver.com</t>
+          <t>yang4550@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1327-6084</t>
+          <t>0507-1319-1270</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 210호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동3층 302호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dinga_nail</t>
+          <t>https://www.instagram.com/jj__nail___</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6045,13 +6061,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +6076,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1879647738</t>
+          <t>2011413114</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1879647738</t>
+          <t>https://m.place.naver.com/place/2011413114</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6082,25 +6098,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>요네일</t>
+          <t>블링루원뷰티</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yunjin0313@naver.com</t>
+          <t>ball_11058@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1462-3543</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 103호</t>
+          <t>인천광역시 서구 청중로478번안길 6 아트프라자 203호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/yo_nailshop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6110,7 +6130,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6131,17 +6151,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>512</v>
+        <v>230</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="R61" t="n">
-        <v>545</v>
+        <v>239</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6150,17 +6170,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1271412561</t>
+          <t>1323823289</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1271412561</t>
+          <t>https://m.place.naver.com/place/1323823289</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6172,34 +6192,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>미드미네일</t>
+          <t>제이네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>dreaming_yjso@naver.com</t>
+          <t>morningapple6@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1309-9513</t>
+          <t>0507-1386-7822</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 23 미드미네일</t>
+          <t>인천광역시 서구 청라에메랄드로 99 B동 1층 026호 Jnail</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kVxoJxj</t>
+          <t>http://www.instagram.com/j_nail21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6220,7 +6240,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6229,14 +6249,14 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="n">
+        <v>13</v>
+      </c>
+      <c r="R62" t="n">
         <v>20</v>
       </c>
-      <c r="R62" t="n">
-        <v>70</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6244,17 +6264,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1581342551</t>
+          <t>1404214241</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581342551</t>
+          <t>https://m.place.naver.com/place/1404214241</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6266,34 +6286,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일,미</t>
+          <t>민블리네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>specialjee@naver.com</t>
+          <t>eun301010_@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1476-4143</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로233번길 3-4 103호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-8 . 1층 109호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ytyub</t>
+          <t>https://www.instagram.com/nail_thelove?igsh=MTloYm44ZHd2OHZmdw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6314,7 +6330,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6323,13 +6339,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>357</v>
+        <v>46</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>395</v>
+        <v>50</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6338,17 +6354,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1645376518</t>
+          <t>1370458509</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1645376518</t>
+          <t>https://m.place.naver.com/place/1370458509</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6360,30 +6376,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일클로버</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>츄네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>chuu_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1309-5041</t>
+          <t>0507-1355-7059</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 103동 211호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
+          <t>http://pf.kakao.com/_DyBJs</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6404,7 +6424,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6413,13 +6433,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>221</v>
+        <v>48</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6428,17 +6448,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1024146721</t>
+          <t>1673851812</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024146721</t>
+          <t>https://m.place.naver.com/place/1673851812</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6450,35 +6470,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>와우뷰티 청라점</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>도르네일</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>bnm4818@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1323-1043</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 레이크봄 상가 212호</t>
+          <t>인천광역시 서구 청라에메랄드로102번길 8-22 미라클프라자1층 104호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/w0woo_nail?igsh=MW03cXVqYmF4MHpvMQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://toss.place/_lb/hCmFKNexK</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6503,13 +6523,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>92</v>
+        <v>733</v>
       </c>
       <c r="Q65" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R65" t="n">
-        <v>141</v>
+        <v>787</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6518,17 +6538,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1012993987</t>
+          <t>1001824596</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012993987</t>
+          <t>https://m.place.naver.com/place/1001824596</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6540,29 +6560,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>굳띵네일</t>
+          <t>네일, 안느</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hahahaam@naver.com</t>
+          <t>gkswngml3594@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>070-4247-1016</t>
+          <t>0507-1403-9410</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로163번길 12 1층</t>
+          <t>인천광역시 서구 푸른로7번길 14 1층 102호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodthing.nail</t>
+          <t>https://www.instagram.com/0n_anne</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6597,13 +6617,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="Q66" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R66" t="n">
-        <v>66</v>
+        <v>233</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6612,17 +6632,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1194539605</t>
+          <t>1256153031</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194539605</t>
+          <t>https://m.place.naver.com/place/1256153031</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6634,29 +6654,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일바이윰 청라본점</t>
+          <t>인생네일 청라본점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>db-king@naver.com</t>
+          <t>askflclsrna@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1409-8945</t>
+          <t>0507-1301-5228</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로42번길 5-5 1층 101호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-15 센트럴시티 223호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by.yoom</t>
+          <t>https://www.instagram.com/life_nail_salon</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6691,13 +6711,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>156</v>
+        <v>351</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R67" t="n">
-        <v>158</v>
+        <v>362</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6706,17 +6726,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1031692471</t>
+          <t>1764464663</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031692471</t>
+          <t>https://m.place.naver.com/place/1764464663</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6728,34 +6748,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>트윈스네일</t>
+          <t>네일에딧</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>form2030@naver.com</t>
+          <t>byddooroo@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1309-9545</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 1층 122호 트윈스네일</t>
+          <t>인천광역시 서구 청라라임로 51 1층 104호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/form2030</t>
+          <t>http://pf.kakao.com/_dZxhxcn</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6765,7 +6781,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6785,13 +6801,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>105</v>
+        <v>804</v>
       </c>
       <c r="Q68" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="R68" t="n">
-        <v>132</v>
+        <v>810</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6800,17 +6816,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1102751111</t>
+          <t>2041818773</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102751111</t>
+          <t>https://m.place.naver.com/place/2041818773</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6822,29 +6838,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>어바웃뷰티 왁싱네일 청라 가정점</t>
+          <t>네일클로버</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01192291122@naver.com</t>
+          <t>haery_kim@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1338-0068</t>
+          <t>0507-1309-5041</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 새오개로111번안길 28 2층 어바웃뷰티왁싱네일</t>
+          <t>인천광역시 서구 청라에메랄드로 79 1층 C11호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/01192291122</t>
+          <t>https://www.instagram.com/nailclover_cho/profilecard/?igsh=MXE0eWNxazc4eWVubQ==</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6859,7 +6875,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6875,17 +6891,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>907</v>
+        <v>214</v>
       </c>
       <c r="Q69" t="n">
-        <v>380</v>
+        <v>8</v>
       </c>
       <c r="R69" t="n">
-        <v>1287</v>
+        <v>222</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6894,17 +6910,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1868333219</t>
+          <t>1024146721</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868333219</t>
+          <t>https://m.place.naver.com/place/1024146721</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -6916,29 +6932,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>뷰티라운지케이 네일속눈썹피부 청라가정점</t>
+          <t>로미네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>beautylounge-k@naver.com</t>
+          <t>0rominail0@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1467-7707</t>
+          <t>0507-1443-7127</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 11-3 1층 뷰티라운지케이</t>
+          <t>인천광역시 서구 청라에메랄드로 99 1층 091호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautyloungek</t>
+          <t>https://www.instagram.com/ro.mi_nail</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6973,13 +6989,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="Q70" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6988,17 +7004,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1706279657</t>
+          <t>2072431299</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1706279657</t>
+          <t>https://m.place.naver.com/place/2072431299</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7010,34 +7026,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>마이즈네일</t>
+          <t>레푸스 청라점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>flyue@naver.com</t>
+          <t>dldeoqkr@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1417-2584</t>
+          <t>0507-1337-0812</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 19 . 1층 마이즈네일</t>
+          <t>인천광역시 서구 청라라임로 71 진영메디피아 208호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_BMRfG</t>
+          <t>https://open.kakao.com/o/sYKKOFJe</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7067,13 +7083,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>180</v>
+        <v>302</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="R71" t="n">
-        <v>184</v>
+        <v>370</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7082,17 +7098,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1176695071</t>
+          <t>1742485791</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176695071</t>
+          <t>https://m.place.naver.com/place/1742485791</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7104,29 +7120,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>랑띠에네일 물어뜯는 손톱연장 노가시스템</t>
+          <t>네일드림</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>dlgufl0924@naver.com</t>
+          <t>shsally0122@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1408-0807</t>
+          <t>0507-1335-1809</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가 A동 108호 랑띠에네일</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 2층 218호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lantienail_official/</t>
+          <t>http://instagram.com/naild_lim</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7161,13 +7177,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>610</v>
+        <v>356</v>
       </c>
       <c r="Q72" t="n">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="R72" t="n">
-        <v>828</v>
+        <v>364</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7192,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>37922472</t>
+          <t>1192065742</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37922472</t>
+          <t>https://m.place.naver.com/place/1192065742</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7198,29 +7214,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일또온나 청라점</t>
+          <t>팡네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2xmania2xj@naver.com</t>
+          <t>nailppang@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1338-3150</t>
+          <t>0507-1367-8073</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-16 101동 203호</t>
+          <t>인천광역시 서구 염곡로498번길 6 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_tto_onna</t>
+          <t>https://www.instagram.com/pang___nail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7255,13 +7271,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="Q73" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="R73" t="n">
-        <v>310</v>
+        <v>40</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7270,17 +7286,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1546215593</t>
+          <t>2066386524</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1546215593</t>
+          <t>https://m.place.naver.com/place/2066386524</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7292,29 +7308,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>감성네일</t>
+          <t>쏠네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gamseongnail@naver.com</t>
+          <t>hansol5992@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1424-4545</t>
+          <t>070-7612-9500</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 b동 1층 38호</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매5동 203호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gam_seongnail/</t>
+          <t>https://www.instagram.com/ssol_nail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7349,13 +7365,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>449</v>
+        <v>73</v>
       </c>
       <c r="Q74" t="n">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>614</v>
+        <v>77</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7364,17 +7380,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1382824710</t>
+          <t>1187656534</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382824710</t>
+          <t>https://m.place.naver.com/place/1187656534</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7386,34 +7402,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>츄네일</t>
+          <t>오늘의 네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>chuu_nail@naver.com</t>
+          <t>redcherry88@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1355-7059</t>
+          <t>0507-1484-2578</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 103동 211호</t>
+          <t>인천광역시 서구 담지로8번길 7-10 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DyBJs</t>
+          <t>https://www.instagram.com/0neulnail</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7434,7 +7450,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7443,13 +7459,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7458,17 +7474,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1673851812</t>
+          <t>1312212877</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673851812</t>
+          <t>https://m.place.naver.com/place/1312212877</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -7480,29 +7496,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일델루나</t>
+          <t>포네하네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>eatingzzz@naver.com</t>
+          <t>forestnh@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1358-7017</t>
+          <t>0507-1400-8523</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 163 정문상가 B06 네일델루나</t>
+          <t>인천광역시 서구 청라라임로122번길 13 1층 101호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_delluna</t>
+          <t>https://blog.naver.com/forestnh</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7517,7 +7533,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7537,13 +7553,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1534</v>
+        <v>337</v>
       </c>
       <c r="Q76" t="n">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="R76" t="n">
-        <v>1549</v>
+        <v>453</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7552,17 +7568,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1852644091</t>
+          <t>1672609930</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852644091</t>
+          <t>https://m.place.naver.com/place/1672609930</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
